--- a/tame_output/ON/bt/strategyON_20240525.xlsx
+++ b/tame_output/ON/bt/strategyON_20240525.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>57.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.1%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-51.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-608.4%</t>
+          <t>-605.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-273.7%</t>
+          <t>-272.6%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-37.3%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-231.2%</t>
+          <t>-228.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-169.1%</t>
+          <t>-167.5%</t>
         </is>
       </c>
     </row>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009943</v>
+        <v>3.843270952009944</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046994</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46838,16 +46838,16 @@
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.518563364175138</v>
+        <v>-4.423364390560595</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.146359086035403</v>
+        <v>1.18443867548122</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1381459049019005</v>
+        <v>-0.04294693128735649</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.871253313078066</v>
+        <v>2.928372697246792</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.456265365399016</v>
+        <v>-4.361066391784473</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.237613839342673</v>
+        <v>1.27569342878849</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1381459049019005</v>
+        <v>-0.04294693128735649</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.937588866874886</v>
+        <v>2.994708251043613</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.254475167733858</v>
+        <v>-4.159276194119315</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.026910790798134</v>
+        <v>1.064990380243951</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.05987228726725391</v>
+        <v>0.1550712608817979</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.764980654565777</v>
+        <v>2.822100038734503</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.194584486091265</v>
+        <v>-4.099385512476721</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.121157295777346</v>
+        <v>1.159236885223164</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.1197629689098474</v>
+        <v>0.2149619425243914</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.871205295873509</v>
+        <v>2.928324680042235</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.813975250643643</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.292325030716239</v>
+        <v>-4.197126057101696</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.0966888140434</v>
+        <v>1.134768403489218</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.1038736907768672</v>
+        <v>0.1990726643914112</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.876299465109764</v>
+        <v>2.93341884927849</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.895365960753426</v>
+        <v>3.859406994851343</v>
       </c>
       <c r="C1974" t="n">
         <v>2.812511231468315</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.468518913777274</v>
+        <v>-4.441026625714402</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.024747241643658</v>
+        <v>1.035744156868807</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.07232019228416781</v>
+        <v>-0.04482790422129507</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.769119116097814</v>
+        <v>2.785614488935538</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240525.xlsx
+++ b/tame_output/ON/bt/strategyON_20240525.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>29.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-51.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.1%</t>
+          <t>446.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-605.7%</t>
+          <t>-620.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.1%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-272.6%</t>
+          <t>-278.8%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-228.5%</t>
+          <t>-231.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-167.5%</t>
+          <t>-169.1%</t>
         </is>
       </c>
     </row>
@@ -43635,7 +43635,7 @@
         <v>45292</v>
       </c>
       <c r="B1830" t="n">
-        <v>3.346337136295372</v>
+        <v>3.346337136295373</v>
       </c>
       <c r="C1830" t="n">
         <v>3.127238527942291</v>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.3014133930858</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705546</v>
+        <v>3.311607601705547</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045694</v>
+        <v>3.317575502045695</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831155</v>
+        <v>3.320996253831156</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355691</v>
+        <v>3.311888301355693</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279816</v>
+        <v>3.385382209279817</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511407</v>
+        <v>3.367379938511408</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153011</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382195</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776673</v>
+        <v>3.500446096776674</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.49684832919989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234399</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860588</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767402</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792546</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567237</v>
+        <v>3.800825778567239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487765</v>
+        <v>3.789307536487767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309719</v>
+        <v>3.833249172309721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858722</v>
+        <v>3.839370871858724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096467</v>
+        <v>3.856158176096469</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255784</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860426</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389908</v>
+        <v>3.81245010338991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749181</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009944</v>
+        <v>3.843270952009943</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144514</v>
+        <v>3.762643902144516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473597</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675891</v>
+        <v>3.746038950675893</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695437</v>
+        <v>3.765020747695439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581288</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734157</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212293</v>
+        <v>3.786946382212296</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786041</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279496</v>
+        <v>3.733387025279499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030424</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942736</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268534</v>
+        <v>3.743044028268536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968858</v>
+        <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175318</v>
+        <v>3.64306604617532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199263</v>
+        <v>3.682712735199265</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660762</v>
+        <v>3.733008865660763</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383417</v>
+        <v>3.741170494383419</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002478</v>
+        <v>3.75114362200248</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263895</v>
+        <v>3.741324873263896</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481227</v>
+        <v>3.750725801481229</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452222</v>
+        <v>3.716988143452224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979529</v>
+        <v>3.737023032979531</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285451</v>
+        <v>3.705568086285454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.34940387318133</v>
+        <v>-4.474354458741302</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9513853404476695</v>
+        <v>0.901405106223681</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2765605220859033</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848099</v>
+        <v>3.709506867848102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.330365745474033</v>
+        <v>-4.455316331034004</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9555253107388335</v>
+        <v>0.9055450765148449</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3347441334170979</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106089760125</v>
+        <v>3.731060897601252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.361492376624652</v>
+        <v>-4.486442962184623</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.120656527217267</v>
+        <v>1.070676292993278</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3347441334170979</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537861</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.413812757225443</v>
+        <v>-4.538763342785415</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.100561703963084</v>
+        <v>1.050581469739095</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.2997972734082257</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259117</v>
+        <v>3.787422005259119</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.558135663150362</v>
+        <v>-4.683086248710334</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.048841071990042</v>
+        <v>0.9988608377660533</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.2997972734082257</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989902</v>
+        <v>3.781497674989904</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.41039269291536</v>
+        <v>-4.535343278475331</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.187090907876065</v>
+        <v>1.137110673652076</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.1319899161733425</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651163</v>
+        <v>3.802242353651165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.512407375446581</v>
+        <v>-4.637357961006552</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.149078656395057</v>
+        <v>1.099098422171069</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.1319899161733425</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864723</v>
+        <v>3.805605409864724</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.375798031352488</v>
+        <v>-4.50074861691246</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.204384742424353</v>
+        <v>1.154404508200364</v>
       </c>
       <c r="F1968" t="n">
         <v>0.00461942792074993</v>
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823621936061</v>
+        <v>3.798236219360613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.423364390560595</v>
+        <v>-4.64351394973511</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.18443867548122</v>
+        <v>1.096378851811414</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.04294693128735649</v>
+        <v>-0.1381459049019005</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.928372697246792</v>
+        <v>2.871253313078066</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86735906126842</v>
+        <v>3.867359061268422</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.361066391784473</v>
+        <v>-4.581215950958987</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.27569342878849</v>
+        <v>1.187633605118684</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.04294693128735649</v>
+        <v>-0.1381459049019005</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.994708251043613</v>
+        <v>2.937588866874886</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462184</v>
+        <v>3.848725564462185</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.159276194119315</v>
+        <v>-4.379425753293829</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.064990380243951</v>
+        <v>0.9769305565741453</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.1550712608817979</v>
+        <v>0.05987228726725391</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.822100038734503</v>
+        <v>2.764980654565777</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841441242322418</v>
+        <v>3.84144124232242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.099385512476721</v>
+        <v>-4.319535071651236</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.159236885223164</v>
+        <v>1.071177061553358</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.2149619425243914</v>
+        <v>0.1197629689098474</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.928324680042235</v>
+        <v>2.871205295873509</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819059724789539</v>
+        <v>3.81905972478954</v>
       </c>
       <c r="C1973" t="n">
         <v>2.813975250643643</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.197126057101696</v>
+        <v>-4.417275616276211</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.134768403489218</v>
+        <v>1.046708579819412</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.1990726643914112</v>
+        <v>0.1038736907768672</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.93341884927849</v>
+        <v>2.876299465109764</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.859406994851343</v>
+        <v>3.579720322684759</v>
       </c>
       <c r="C1974" t="n">
         <v>2.812511231468315</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.441026625714402</v>
+        <v>-4.59361337639914</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.035744156868807</v>
+        <v>0.9747094565949117</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.04482790422129507</v>
+        <v>-0.0724640693460622</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.785614488935538</v>
+        <v>2.769032789860678</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240525.xlsx
+++ b/tame_output/ON/bt/strategyON_20240525.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>56.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.2%</t>
+          <t>127.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-51.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-73.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>446.2%</t>
+          <t>449.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-620.9%</t>
+          <t>-600.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-37.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-278.8%</t>
+          <t>-270.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-38.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-231.2%</t>
+          <t>-230.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-169.1%</t>
+          <t>-168.5%</t>
         </is>
       </c>
     </row>
@@ -43635,7 +43635,7 @@
         <v>45292</v>
       </c>
       <c r="B1830" t="n">
-        <v>3.346337136295373</v>
+        <v>3.346337136295372</v>
       </c>
       <c r="C1830" t="n">
         <v>3.127238527942291</v>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.3014133930858</v>
+        <v>3.301413393085799</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705547</v>
+        <v>3.311607601705546</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045695</v>
+        <v>3.317575502045694</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831156</v>
+        <v>3.320996253831155</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355693</v>
+        <v>3.311888301355691</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279817</v>
+        <v>3.385382209279816</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511408</v>
+        <v>3.367379938511407</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386097</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998565</v>
+        <v>3.367370539998564</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082129</v>
+        <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757927</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611699</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49684832919989</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910633</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078602</v>
+        <v>3.4900556660786</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234399</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262048</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245010338991</v>
+        <v>3.812450103389912</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481494</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102776</v>
+        <v>3.773761647102778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353068</v>
+        <v>3.76461430435307</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544778</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712287</v>
+        <v>3.797691308712289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837677</v>
+        <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349958</v>
+        <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972332</v>
+        <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145931</v>
+        <v>3.818665376145933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009943</v>
+        <v>3.843270952009945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.845043810966259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144516</v>
+        <v>3.762643902144518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473597</v>
+        <v>3.743216620473599</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978365</v>
+        <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887698</v>
+        <v>3.7109031558877</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675893</v>
+        <v>3.746038950675895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695439</v>
+        <v>3.76502074769544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.773206721581292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212296</v>
+        <v>3.786946382212297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279499</v>
+        <v>3.733387025279501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268536</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968861</v>
+        <v>3.689594264968863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306604617532</v>
+        <v>3.643066046175323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199265</v>
+        <v>3.682712735199267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660763</v>
+        <v>3.733008865660766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383419</v>
+        <v>3.741170494383422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.75114362200248</v>
+        <v>3.751143622002482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263896</v>
+        <v>3.741324873263899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481229</v>
+        <v>3.750725801481232</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452224</v>
+        <v>3.716988143452227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979531</v>
+        <v>3.737023032979534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230806</v>
+        <v>3.702305879230809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285454</v>
+        <v>3.705568086285456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.474354458741302</v>
+        <v>-4.34940387318133</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.901405106223681</v>
+        <v>0.9513853404476695</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2765605220859033</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848102</v>
+        <v>3.709506867848104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.455316331034004</v>
+        <v>-4.330365745474033</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9055450765148449</v>
+        <v>0.9555253107388335</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3347441334170979</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601252</v>
+        <v>3.731060897601255</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.486442962184623</v>
+        <v>-4.361492376624652</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.070676292993278</v>
+        <v>1.120656527217267</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3347441334170979</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.538763342785415</v>
+        <v>-4.413812757225443</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.050581469739095</v>
+        <v>1.100561703963084</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.2997972734082257</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259119</v>
+        <v>3.787422005259121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.683086248710334</v>
+        <v>-4.558135663150362</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9988608377660533</v>
+        <v>1.048841071990042</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.2997972734082257</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989904</v>
+        <v>3.781497674989907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.535343278475331</v>
+        <v>-4.41039269291536</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.137110673652076</v>
+        <v>1.187090907876065</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.1319899161733425</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651165</v>
+        <v>3.802242353651168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.637357961006552</v>
+        <v>-4.512407375446581</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.099098422171069</v>
+        <v>1.149078656395057</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.1319899161733425</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864724</v>
+        <v>3.805605409864728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.50074861691246</v>
+        <v>-4.375798031352488</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.154404508200364</v>
+        <v>1.204384742424353</v>
       </c>
       <c r="F1968" t="n">
         <v>0.00461942792074993</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360613</v>
+        <v>3.798236219360616</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.64351394973511</v>
+        <v>-4.518563364175138</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.096378851811414</v>
+        <v>1.146359086035403</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.1381459049019005</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268422</v>
+        <v>3.867359061268425</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.581215950958987</v>
+        <v>-4.456265365399016</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.187633605118684</v>
+        <v>1.237613839342673</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.1381459049019005</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462185</v>
+        <v>3.848725564462189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.379425753293829</v>
+        <v>-4.254475167733858</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9769305565741453</v>
+        <v>1.026910790798134</v>
       </c>
       <c r="F1971" t="n">
         <v>0.05987228726725391</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144124232242</v>
+        <v>3.841441242322423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.319535071651236</v>
+        <v>-4.194584486091265</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.071177061553358</v>
+        <v>1.121157295777346</v>
       </c>
       <c r="F1972" t="n">
         <v>0.1197629689098474</v>
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81905972478954</v>
+        <v>3.819059724789544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.813975250643643</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.417275616276211</v>
+        <v>-4.21388325641699</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.046708579819412</v>
+        <v>1.1280655237631</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.1038736907768672</v>
+        <v>0.1146586831445777</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.876299465109764</v>
+        <v>2.88277046053039</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.579720322684759</v>
+        <v>3.85020323646099</v>
       </c>
       <c r="C1974" t="n">
         <v>2.812511231468315</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.59361337639914</v>
+        <v>-4.390221016539919</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9747094565949117</v>
+        <v>1.0560664005386</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.0724640693460622</v>
+        <v>-0.06167907697835168</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.769032789860678</v>
+        <v>2.775503785281304</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240525.xlsx
+++ b/tame_output/ON/bt/strategyON_20240525.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>19.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-54.2%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.0%</t>
+          <t>126.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.0%</t>
+          <t>-51.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.3%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.1%</t>
+          <t>444.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-600.6%</t>
+          <t>-620.5%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-38.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-21.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-270.6%</t>
+          <t>-278.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-23.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-38.0%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-230.2%</t>
+          <t>-221.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-168.5%</t>
+          <t>-189.3%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1974"/>
+  <dimension ref="A1:G1975"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860588</v>
+        <v>3.493712438860587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767402</v>
+        <v>3.492098065767401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792546</v>
+        <v>3.573670449792545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628924</v>
+        <v>3.600034689628923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567239</v>
+        <v>3.800825778567237</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487767</v>
+        <v>3.789307536487765</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309721</v>
+        <v>3.833249172309719</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858724</v>
+        <v>3.839370871858722</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096469</v>
+        <v>3.856158176096467</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75387899643099</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963421</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192819</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389912</v>
+        <v>3.81245010338991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.835954411481494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102778</v>
+        <v>3.773761647102776</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461430435307</v>
+        <v>3.764614304353068</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544778</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712289</v>
+        <v>3.797691308712287</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.821589933837677</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349958</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.848613050972332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145933</v>
+        <v>3.818665376145931</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009945</v>
+        <v>3.843270952009944</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966259</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412105</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144518</v>
+        <v>3.762643902144516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473599</v>
+        <v>3.743216620473597</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>3.714175563978365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109031558877</v>
+        <v>3.710903155887698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675895</v>
+        <v>3.746038950675893</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502074769544</v>
+        <v>3.765020747695439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581292</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.78434037673416</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212297</v>
+        <v>3.786946382212296</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786045</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.264760805820979</v>
+        <v>-4.430037782178848</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.097092048265381</v>
+        <v>1.030981257722233</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2113693691908228</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279501</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.171950324370119</v>
+        <v>-4.337227300727989</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.06348893273709</v>
+        <v>0.9973781421939425</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1185588877399635</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.123387272149089</v>
+        <v>-4.288664248506959</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.084787629550103</v>
+        <v>1.018676839006955</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.06999583551893329</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.010716053912839</v>
+        <v>-4.175993030270709</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.124931825356326</v>
+        <v>1.058821034813178</v>
       </c>
       <c r="F1948" t="n">
         <v>0.04267538271731691</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.898339052730166</v>
+        <v>-4.063616029088036</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.175373921660062</v>
+        <v>1.109263131116915</v>
       </c>
       <c r="F1949" t="n">
         <v>0.04267538271731691</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968863</v>
+        <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.096573621616897</v>
+        <v>-4.261850597974767</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.107577295873909</v>
+        <v>1.041466505330761</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1555591861694137</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175323</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.179574902642176</v>
+        <v>-4.344851879000045</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9127325034644511</v>
+        <v>0.8466217129213032</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.1741300706965874</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199267</v>
+        <v>3.682712735199265</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.306641908949164</v>
+        <v>-4.471918885307034</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9820553616608616</v>
+        <v>0.9159445711177137</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.1741300706965874</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660766</v>
+        <v>3.733008865660764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.393240491930267</v>
+        <v>-4.558517468288136</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9619289545707432</v>
+        <v>0.8958181640275955</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1741300706965874</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383422</v>
+        <v>3.74117049438342</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.354856829372116</v>
+        <v>-4.520133805729985</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9747018609363725</v>
+        <v>0.9085910703932245</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.1357464081384362</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002482</v>
+        <v>3.751143622002481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.17774049933695</v>
+        <v>-4.343017475694819</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.042277421795741</v>
+        <v>0.976166631252593</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.1357464081384362</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263899</v>
+        <v>3.741324873263897</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.148038375360656</v>
+        <v>-4.313315351718526</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.054841663148171</v>
+        <v>0.9887308726050235</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.1402165333537496</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481232</v>
+        <v>3.75072580148123</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.968662954121888</v>
+        <v>-4.133939930479758</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.120378806950093</v>
+        <v>1.054268016406945</v>
       </c>
       <c r="F1957" t="n">
         <v>0.01656022481696906</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452227</v>
+        <v>3.716988143452225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.013677167642495</v>
+        <v>-4.178954144000365</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.08318057687344</v>
+        <v>1.017069786330292</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.01378867049763555</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979534</v>
+        <v>3.737023032979532</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.28068167791493</v>
+        <v>-4.4459586542728</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9820703351034117</v>
+        <v>0.9159595445602637</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.2081517085405841</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230809</v>
+        <v>3.702305879230807</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.381879459352103</v>
+        <v>-4.547156435709972</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.940795144425044</v>
+        <v>0.874684353881896</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2765605220859033</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285456</v>
+        <v>3.705568086285455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.34940387318133</v>
+        <v>-4.640829077461252</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9513853404476695</v>
+        <v>0.8348152587357012</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2765605220859033</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848104</v>
+        <v>3.709506867848103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.330365745474033</v>
+        <v>-4.621790949753954</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9555253107388335</v>
+        <v>0.8389552290268649</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3347441334170979</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601255</v>
+        <v>3.731060897601254</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.361492376624652</v>
+        <v>-4.652917580904573</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.120656527217267</v>
+        <v>1.004086445505298</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3347441334170979</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537866</v>
+        <v>3.722443786537865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.413812757225443</v>
+        <v>-4.705237961505365</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.100561703963084</v>
+        <v>0.9839916222511149</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.2997972734082257</v>
@@ -46746,10 +46746,10 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.558135663150362</v>
+        <v>-4.849560867430283</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.048841071990042</v>
+        <v>0.9322709902780733</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.2997972734082257</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989907</v>
+        <v>3.781497674989906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.41039269291536</v>
+        <v>-4.701817897195281</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.187090907876065</v>
+        <v>1.070520826164096</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.1319899161733425</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651168</v>
+        <v>3.802242353651167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.512407375446581</v>
+        <v>-4.803832579726502</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.149078656395057</v>
+        <v>1.032508574683089</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.1319899161733425</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864728</v>
+        <v>3.805605409864726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.375798031352488</v>
+        <v>-4.667223235632409</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.204384742424353</v>
+        <v>1.087814660712384</v>
       </c>
       <c r="F1968" t="n">
         <v>0.00461942792074993</v>
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360616</v>
+        <v>3.798236219360614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.518563364175138</v>
+        <v>-4.714789594840516</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.146359086035403</v>
+        <v>1.067868593769252</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1381459049019005</v>
+        <v>-0.04294693128735649</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.871253313078066</v>
+        <v>2.928372697246792</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268425</v>
+        <v>3.867359061268424</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.456265365399016</v>
+        <v>-4.652491596064394</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.237613839342673</v>
+        <v>1.159123347076522</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1381459049019005</v>
+        <v>-0.04294693128735649</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.937588866874886</v>
+        <v>2.994708251043613</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462189</v>
+        <v>3.848725564462187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.254475167733858</v>
+        <v>-4.450701398399236</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.026910790798134</v>
+        <v>0.9484202985319827</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.05987228726725391</v>
+        <v>0.1550712608817979</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.764980654565777</v>
+        <v>2.822100038734503</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841441242322423</v>
+        <v>3.841441242322421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.194584486091265</v>
+        <v>-4.390810716756643</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.121157295777346</v>
+        <v>1.042666803511195</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.1197629689098474</v>
+        <v>0.2149619425243914</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.871205295873509</v>
+        <v>2.928324680042235</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819059724789544</v>
+        <v>3.819059724789542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.813975250643643</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.21388325641699</v>
+        <v>-4.412844827181855</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.1280655237631</v>
+        <v>1.048480895457154</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.1146586831445777</v>
+        <v>0.2063767873821524</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.88277046053039</v>
+        <v>2.937801323072935</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,45 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.85020323646099</v>
+        <v>3.831815456959379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.812511231468315</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.390221016539919</v>
+        <v>-4.589182587304784</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.0560664005386</v>
+        <v>0.976481772232654</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.06167907697835168</v>
+        <v>0.03003902725922303</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.775503785281304</v>
+        <v>2.830534647823849</v>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" s="2" t="n">
+        <v>45437</v>
+      </c>
+      <c r="B1975" t="n">
+        <v>3.471281734550422</v>
+      </c>
+      <c r="C1975" t="n">
+        <v>2.574672969525396</v>
+      </c>
+      <c r="D1975" t="n">
+        <v>-4.589182587304784</v>
+      </c>
+      <c r="E1975" t="n">
+        <v>0.976481772232654</v>
+      </c>
+      <c r="F1975" t="n">
+        <v>0.03003902725922303</v>
+      </c>
+      <c r="G1975" t="n">
+        <v>2.567736766511764</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240525.xlsx
+++ b/tame_output/ON/bt/strategyON_20240525.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>15.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-54.2%</t>
+          <t>-57.2%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>108.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.7%</t>
+          <t>126.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.1%</t>
+          <t>-52.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.6%</t>
+          <t>443.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-620.5%</t>
+          <t>-662.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.0%</t>
+          <t>-38.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-21.4%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-278.6%</t>
+          <t>-295.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-221.0%</t>
+          <t>-253.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-13.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-189.3%</t>
+          <t>-192.3%</t>
         </is>
       </c>
     </row>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386097</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998564</v>
+        <v>3.367370539998565</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082129</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757927</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706675</v>
+        <v>3.298730590706676</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296842</v>
+        <v>3.299918119296843</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201492</v>
+        <v>3.295507330201493</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153011</v>
+        <v>3.258791981153012</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537432</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382195</v>
+        <v>3.272760131382197</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074626</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.233800325911643</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.2235393782135</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416049</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382332</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495503</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347058</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.28737757613002</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923088</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776674</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900556660786</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880273</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860587</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767401</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792545</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628923</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567237</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487765</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309719</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858722</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096467</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.76317867286043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457899</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.72996614056811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.82854791119282</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245010338991</v>
+        <v>3.812450103389912</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788097</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527529</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481494</v>
+        <v>3.8359544114815</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102776</v>
+        <v>3.773761647102783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353068</v>
+        <v>3.764614304353076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712287</v>
+        <v>3.797691308712295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837677</v>
+        <v>3.821589933837686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349958</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972332</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145931</v>
+        <v>3.81866537614594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009944</v>
+        <v>3.843270952009952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.845043810966261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046996</v>
+        <v>3.791269976046999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412107</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144516</v>
+        <v>3.762643902144519</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.282014686703002</v>
+        <v>-4.423069227337614</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.283077946935659</v>
+        <v>1.226656130681814</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.009505735755486688</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.284484393164808</v>
+        <v>-4.42553893379942</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.282162465724349</v>
+        <v>1.225740649470504</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.01197544221729285</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473597</v>
+        <v>3.743216620473602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.352854579488818</v>
+        <v>-4.49390912012343</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.265821313669447</v>
+        <v>1.209399497415602</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.002699743181077907</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978365</v>
+        <v>3.714175563978371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.461392760404952</v>
+        <v>-4.602447301039564</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.212842749934884</v>
+        <v>1.15642093368104</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.002699743181077907</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887698</v>
+        <v>3.710903155887705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.492385919733658</v>
+        <v>-4.633440460368269</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.025155051243789</v>
+        <v>0.9687332349899447</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.002699743181077907</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675893</v>
+        <v>3.746038950675901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.316911659941189</v>
+        <v>-4.4579662005758</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.099911987152564</v>
+        <v>1.04349017089872</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.002699743181077907</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695439</v>
+        <v>3.765020747695446</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.427847912582438</v>
+        <v>-4.568902453217049</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.031279514857272</v>
+        <v>0.9748576986034274</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.002699743181077907</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.630874490125671</v>
+        <v>-4.771929030760282</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9532002690598842</v>
+        <v>0.8967784528060396</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2057263207243113</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434037673416</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.472948891190378</v>
+        <v>-4.614003431824989</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.026542895066134</v>
+        <v>0.9701210788122892</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2057263207243113</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212296</v>
+        <v>3.786946382212298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.386705428164</v>
+        <v>-4.527759968798612</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.055986550850545</v>
+        <v>0.9995647345967007</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2057263207243113</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.387888512815062</v>
+        <v>-4.528943053449673</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.047289092434646</v>
+        <v>0.9908672761808015</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2113693691908228</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.430037782178848</v>
+        <v>-4.40581534645559</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.030981257722233</v>
+        <v>1.040670232011536</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2113693691908228</v>
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.337227300727989</v>
+        <v>-4.443617851073695</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9973781421939425</v>
+        <v>0.9548219220556602</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1185588877399635</v>
+        <v>-0.2491718738089274</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.661490154154908</v>
+        <v>2.583122362513529</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.288664248506959</v>
+        <v>-4.395054798852665</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.018676839006955</v>
+        <v>0.9761206188686729</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.06999583551893329</v>
+        <v>-0.2006088215878972</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.692501461412126</v>
+        <v>2.614133669770748</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.175993030270709</v>
+        <v>-4.282383580616415</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.058821034813178</v>
+        <v>1.016264814674896</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.04267538271731691</v>
+        <v>-0.08793760335164696</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.755179900865599</v>
+        <v>2.676812109224221</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.063616029088036</v>
+        <v>-4.340983121941723</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.109263131116915</v>
+        <v>0.99831629397544</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.04267538271731691</v>
+        <v>-0.08793760335164696</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.760671196696267</v>
+        <v>2.682303405054888</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968862</v>
+        <v>3.689594264968865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.261850597974767</v>
+        <v>-4.437278743000276</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.041466505330761</v>
+        <v>0.9712952473205578</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1555591861694137</v>
+        <v>-0.1842332244101994</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.653227657132768</v>
+        <v>2.636023234188296</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.643066046175325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.344851879000045</v>
+        <v>-4.520280024025555</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8466217129213032</v>
+        <v>0.7764504549110995</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1741300706965874</v>
+        <v>-0.2028041089373732</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.480440846417117</v>
+        <v>2.463236423472645</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199265</v>
+        <v>3.68271273519927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.471918885307034</v>
+        <v>-4.647347030332543</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9159445711177137</v>
+        <v>0.84577331310751</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1741300706965874</v>
+        <v>-0.2028041089373732</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.600590507136322</v>
+        <v>2.583386084191851</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660764</v>
+        <v>3.73300886566077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.558517468288136</v>
+        <v>-4.733945613313645</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8958181640275955</v>
+        <v>0.8256469060173919</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1741300706965874</v>
+        <v>-0.2028041089373732</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.615103533238645</v>
+        <v>2.597899110294174</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.74117049438342</v>
+        <v>3.741170494383425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.520133805729985</v>
+        <v>-4.695561950755494</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9085910703932245</v>
+        <v>0.8384198123830209</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1357464081384362</v>
+        <v>-0.164420446379222</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.635553172115904</v>
+        <v>2.618348749171433</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002481</v>
+        <v>3.751143622002486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.343017475694819</v>
+        <v>-4.518445620720328</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.976166631252593</v>
+        <v>0.9059953732423893</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1357464081384362</v>
+        <v>-0.164420446379222</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.632282200961206</v>
+        <v>2.615077778016735</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263897</v>
+        <v>3.741324873263903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.313315351718526</v>
+        <v>-4.488743496744035</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9887308726050235</v>
+        <v>0.9185596145948198</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1402165333537496</v>
+        <v>-0.1688905715945354</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.630283517593932</v>
+        <v>2.61307909464946</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.75072580148123</v>
+        <v>3.750725801481236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.133939930479758</v>
+        <v>-4.309368075505267</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.054268016406945</v>
+        <v>0.9840967583967413</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.01656022481696906</v>
+        <v>-0.01211381342381668</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.718136547802777</v>
+        <v>2.700932124858306</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452225</v>
+        <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.178954144000365</v>
+        <v>-4.354382289025873</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.017069786330292</v>
+        <v>0.9468985283200888</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.01378867049763555</v>
+        <v>-0.04246270873842128</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.680734665945604</v>
+        <v>2.663530243001133</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979532</v>
+        <v>3.737023032979538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.4459586542728</v>
+        <v>-4.621386799298308</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9159595445602637</v>
+        <v>0.8457882865500606</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2081517085405841</v>
+        <v>-0.2368257467813699</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.569808405458781</v>
+        <v>2.552603982514309</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230807</v>
+        <v>3.702305879230808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.547156435709972</v>
+        <v>-4.72258458073548</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.874684353881896</v>
+        <v>0.8045130958716928</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2765605220859033</v>
+        <v>-0.3052345603266891</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.52796703922809</v>
+        <v>2.510762616283619</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.640829077461252</v>
+        <v>-4.690108994564708</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8348152587357012</v>
+        <v>0.8151032918943184</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2765605220859033</v>
+        <v>-0.3052345603266891</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.525567000782407</v>
+        <v>2.508362577837936</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.621790949753954</v>
+        <v>-4.671070866857411</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8389552290268649</v>
+        <v>0.8192432621854824</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3347441334170979</v>
+        <v>-0.3634181716578836</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.487181553191935</v>
+        <v>2.469977130247464</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.652917580904573</v>
+        <v>-4.702197498008029</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.004086445505298</v>
+        <v>0.9843744786639155</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3347441334170979</v>
+        <v>-0.3634181716578836</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.664763422130616</v>
+        <v>2.647558999186145</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537865</v>
+        <v>3.722443786537867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.705237961505365</v>
+        <v>-4.754517878608821</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9839916222511149</v>
+        <v>0.9642796554097324</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2997972734082257</v>
+        <v>-0.3284713116490114</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.686564867122073</v>
+        <v>2.669360444177602</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259121</v>
+        <v>3.787422005259124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.849560867430283</v>
+        <v>-4.89884078453374</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9322709902780733</v>
+        <v>0.9125590234366907</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2997972734082257</v>
+        <v>-0.3284713116490114</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.692573397518999</v>
+        <v>2.675368974574527</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989906</v>
+        <v>3.78149767498991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.701817897195281</v>
+        <v>-4.751097814298737</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.070520826164096</v>
+        <v>1.050808859322714</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1319899161733425</v>
+        <v>-0.1606639544141283</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.872410459651951</v>
+        <v>2.855206036707479</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651167</v>
+        <v>3.802242353651172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.803832579726502</v>
+        <v>-4.853112496829959</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.032508574683089</v>
+        <v>1.012796607841706</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1319899161733425</v>
+        <v>-0.1606639544141283</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.875204081183432</v>
+        <v>2.85799965823896</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864726</v>
+        <v>3.805605409864731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.667223235632409</v>
+        <v>-4.716503152735866</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.087814660712384</v>
+        <v>1.068102693871002</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.00461942792074993</v>
+        <v>-0.02405461032003581</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.957832036031546</v>
+        <v>2.940627613087074</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.714789594840516</v>
+        <v>-4.859268485558516</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.067868593769252</v>
+        <v>1.010077037482052</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.04294693128735649</v>
+        <v>-0.1668199431426862</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.928372697246792</v>
+        <v>2.854048890133594</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268424</v>
+        <v>3.867359061268427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.652491596064394</v>
+        <v>-4.796970486782394</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.159123347076522</v>
+        <v>1.101331790789322</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.04294693128735649</v>
+        <v>-0.1668199431426862</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.994708251043613</v>
+        <v>2.920384443930415</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462187</v>
+        <v>3.848725564462193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.450701398399236</v>
+        <v>-4.793258395382968</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9484202985319827</v>
+        <v>0.8113974997384901</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.1550712608817979</v>
+        <v>-0.1611996183602881</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.822100038734503</v>
+        <v>2.632337511189252</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841441242322421</v>
+        <v>3.841441242322422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.390810716756643</v>
+        <v>-4.733367713740375</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.042666803511195</v>
+        <v>0.9056440047177026</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.2149619425243914</v>
+        <v>-0.1013089367176946</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.928324680042235</v>
+        <v>2.738562152496983</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819059724789542</v>
+        <v>3.819059724789549</v>
       </c>
       <c r="C1973" t="n">
         <v>2.813975250643643</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.412844827181855</v>
+        <v>-4.831108258365349</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.048480895457154</v>
+        <v>0.8811755229837563</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.2063767873821524</v>
+        <v>-0.1171982148506748</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.937801323072935</v>
+        <v>2.743656321733239</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831815456959379</v>
+        <v>3.831815456959392</v>
       </c>
       <c r="C1974" t="n">
         <v>2.812511231468315</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.589182587304784</v>
+        <v>-5.007446018488278</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.976481772232654</v>
+        <v>0.8091763997592563</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.03003902725922303</v>
+        <v>-0.2935359749736042</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.830534647823849</v>
+        <v>2.636389646484153</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.471281734550422</v>
+        <v>3.44008805540053</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.574672969525396</v>
+        <v>2.54459412704105</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.589182587304784</v>
+        <v>-5.007446018488278</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.976481772232654</v>
+        <v>0.8091763997592563</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.03003902725922303</v>
+        <v>-0.2935359749736042</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.567736766511764</v>
+        <v>2.537657924027418</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240525.xlsx
+++ b/tame_output/ON/bt/strategyON_20240525.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>61.4%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,42 +824,42 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-57.2%</t>
+          <t>-17.0%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.3%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.5%</t>
+          <t>127.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.0%</t>
+          <t>-50.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>443.7%</t>
+          <t>449.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-662.3%</t>
+          <t>-604.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,42 +1140,42 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.7%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-295.3%</t>
+          <t>-272.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-31.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-253.3%</t>
+          <t>-219.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-192.3%</t>
+          <t>-152.1%</t>
         </is>
       </c>
     </row>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706676</v>
+        <v>3.298730590706675</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296843</v>
+        <v>3.299918119296842</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201493</v>
+        <v>3.295507330201492</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153012</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537432</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382197</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074626</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911643</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.2235393782135</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416049</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382332</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495503</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347058</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.28737757613002</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.787773598453214</v>
+        <v>-6.848615329049017</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3951600887200994</v>
+        <v>0.3708233964817782</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.204165472740211</v>
+        <v>-7.265007203336014</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2265973896141777</v>
+        <v>0.2022606973758565</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.520777415280859</v>
+        <v>-7.581619145876663</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1102113032665977</v>
+        <v>0.08587461102827643</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.866652237265669</v>
+        <v>-7.927493967861471</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.03203906038163096</v>
+        <v>-0.05637575261995176</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.030232115450053</v>
+        <v>-8.091073846045855</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.09906609160038382</v>
+        <v>-0.1234027838387046</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.326893457260251</v>
+        <v>-8.387735187856054</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2139516523952549</v>
+        <v>-0.2382883446335757</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923088</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.531924638034567</v>
+        <v>-8.59276636863037</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2999904292393847</v>
+        <v>-0.3243271214777055</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.914926026777199</v>
+        <v>-8.975767757373001</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4532930860580211</v>
+        <v>-0.4776297782963419</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.096795817762233</v>
+        <v>-9.157637548358036</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5234694864806047</v>
+        <v>-0.5478061787189259</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.739549887119858</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.456326140266235</v>
+        <v>-9.517167870862037</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.661931312184155</v>
+        <v>-0.6862680044224763</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.739549887119858</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.506675203720457</v>
+        <v>-9.567516934316259</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6741549176086665</v>
+        <v>-0.6984916098469873</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.78989895057408</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776674</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.604294481141853</v>
+        <v>-9.665136211737655</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.710160877955456</v>
+        <v>-0.7344975701937773</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.887518227995477</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.600603556185442</v>
+        <v>-9.661445286781245</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7086845079728916</v>
+        <v>-0.7330212002112129</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.887518227995477</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.804861731515306</v>
+        <v>-9.865703462111108</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.784874580986195</v>
+        <v>-0.8092112732245158</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.015157172609466</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.946671505722094</v>
+        <v>-10.0075132363179</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8371159361844742</v>
+        <v>-0.861452628422795</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.186435970255041</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.873201674054645</v>
+        <v>-9.934043404650447</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7923563020240731</v>
+        <v>-0.8166929942623944</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.112966138587593</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.04832609144119</v>
+        <v>-10.10916782203699</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8478508482311735</v>
+        <v>-0.8721875404694952</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.288090555974136</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.28277818545568</v>
+        <v>-10.34361991605148</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9488508507385656</v>
+        <v>-0.9731875429768864</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.288090555974136</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.57058202999292</v>
+        <v>-10.63142376058872</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.070644579327438</v>
+        <v>-1.094981271565759</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.575894400511375</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.62336818559324</v>
+        <v>-10.68420991618905</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.090643251729012</v>
+        <v>-1.114979943967333</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.671569887093772</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4920980657674</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.85539710532951</v>
+        <v>-10.91623883592531</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.180761090994402</v>
+        <v>-1.205097783232723</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.733582584282195</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.80338159136069</v>
+        <v>-10.86422332195649</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.155964549720475</v>
+        <v>-1.180301241958797</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.733582584282195</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628922</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.94505343308481</v>
+        <v>-11.00589516368061</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.214108513308865</v>
+        <v>-1.238445205547187</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.733582584282195</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.89546258865998</v>
+        <v>-10.95630431925578</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.179218765374059</v>
+        <v>-1.20355545761238</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.683991739857361</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.69631048142288</v>
+        <v>-10.75715221201868</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.112609056125903</v>
+        <v>-1.136945748364224</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.518669213907548</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.47046532870347</v>
+        <v>-10.53130705929927</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.012691922001931</v>
+        <v>-1.037028614240251</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.476742538320384</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.34588667236588</v>
+        <v>-10.40672840296168</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9617213149108346</v>
+        <v>-0.9860580071491545</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.476742538320384</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.39878196041016</v>
+        <v>-10.45962369100596</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9802456559664412</v>
+        <v>-1.004582348204762</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.471787192231938</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.11487322948141</v>
+        <v>-10.17571496007722</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8609484593563055</v>
+        <v>-0.8852851515946254</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.471787192231938</v>
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.04350683687177</v>
+        <v>-10.15272583697049</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8421391647063121</v>
+        <v>-0.8858267647458016</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.40042079962229</v>
+        <v>-2.448798069125213</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.735367514582769</v>
+        <v>1.706341152881015</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702412</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.779669969667697</v>
+        <v>-9.888888969766422</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7464878991375916</v>
+        <v>-0.7901754991770811</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.40042079962229</v>
+        <v>-2.448798069125213</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.725484033269861</v>
+        <v>1.696457671568107</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906228</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.5124281687993</v>
+        <v>-9.621647168898024</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6414257392896059</v>
+        <v>-0.6851133393290958</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.40042079962229</v>
+        <v>-2.448798069125213</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.723649472770487</v>
+        <v>1.694623111068734</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.414521130122809</v>
+        <v>-9.523740130221533</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6025632387924706</v>
+        <v>-0.6462508388319601</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.332435049761734</v>
+        <v>-2.380812319264657</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.764140607713361</v>
+        <v>1.735114246011607</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567238</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.390567589146851</v>
+        <v>-9.499786589245575</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5923133162565937</v>
+        <v>-0.6360009162960836</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.308481508785776</v>
+        <v>-2.356858778288699</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.779181238444429</v>
+        <v>1.750154876742675</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.126507650824054</v>
+        <v>-9.235726650922778</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.4999496570892275</v>
+        <v>-0.5436372571287169</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.04442157046298</v>
+        <v>-2.092798839965903</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.924356885276354</v>
+        <v>1.895330523574601</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.419428027319217</v>
+        <v>-8.528647027417941</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.219904841347593</v>
+        <v>-0.2635924413870829</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.04442157046298</v>
+        <v>-2.092798839965903</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.921569851616053</v>
+        <v>1.8925434899143</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.379243728953027</v>
+        <v>-8.488462729051751</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2034874981132755</v>
+        <v>-0.2471750981527654</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.004237272096789</v>
+        <v>-2.052614541599712</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.946024054523609</v>
+        <v>1.916997692821855</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.299173933415222</v>
+        <v>-8.408392933513946</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.172092758677397</v>
+        <v>-0.2157803587168865</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.924167476558985</v>
+        <v>-1.972544746061908</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.993432753067048</v>
+        <v>1.964406391365295</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.065692711185623</v>
+        <v>-8.174911711284349</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.07077584094770462</v>
+        <v>-0.114463440987195</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.690686254329387</v>
+        <v>-1.739063523832309</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.14144591524266</v>
+        <v>2.112419553540906</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.916026320178108</v>
+        <v>-8.025245320276834</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.01380149485765791</v>
+        <v>-0.05748909489714871</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.597782763086851</v>
+        <v>-1.646160032589773</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.194295799675222</v>
+        <v>2.165269437973468</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.783750846547221</v>
+        <v>-7.892969846645948</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.03447618134172359</v>
+        <v>-0.009211418697767204</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.465507289455964</v>
+        <v>-1.513884558958887</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.269028570600781</v>
+        <v>2.240002208899028</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.593151171874069</v>
+        <v>-7.702370171972795</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1135311118986215</v>
+        <v>0.06984351185913074</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.274907614782811</v>
+        <v>-1.323284884285734</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.38620343609231</v>
+        <v>2.357177074390556</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.344151373190487</v>
+        <v>-7.453370373289214</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2260373725957128</v>
+        <v>0.182349772556222</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.274907614782811</v>
+        <v>-1.323284884285734</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.399109777315968</v>
+        <v>2.370083415614215</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077647</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.449741362963592</v>
+        <v>-7.558960363062319</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.05582544708725212</v>
+        <v>0.01213784704776133</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.380497604555916</v>
+        <v>-1.428874874058838</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.207779853852887</v>
+        <v>2.178753492151134</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.468476265082189</v>
+        <v>-7.577695265180916</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.09687582811689976</v>
+        <v>0.05318822807740897</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.380497604555916</v>
+        <v>-1.428874874058838</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.256324195729974</v>
+        <v>2.22729783402822</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.32053622367459</v>
+        <v>-7.429755223773316</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.03617292199177191</v>
+        <v>-0.007514678047718881</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.360176688647358</v>
+        <v>-1.408553958150281</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.148637822586941</v>
+        <v>2.119611460885187</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.303378073543295</v>
+        <v>-7.412597073642022</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.03432219579081153</v>
+        <v>-0.009365404248679265</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.343018538516064</v>
+        <v>-1.391395808018986</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.150218726412239</v>
+        <v>2.121192364710486</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.259829666772605</v>
+        <v>-7.369048666871332</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.04478094640399455</v>
+        <v>0.001093346364503756</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.343018538516064</v>
+        <v>-1.391395808018986</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.143258114317146</v>
+        <v>2.114231752615392</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963422</v>
+        <v>3.782918957963421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.017681273318747</v>
+        <v>-7.126900273417474</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1561026581666809</v>
+        <v>0.1124150581271901</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.343018538516064</v>
+        <v>-1.391395808018986</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.157720468698289</v>
+        <v>2.128694106996535</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.82854791119282</v>
+        <v>3.828547911192819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.954451901550398</v>
+        <v>-7.063670901649125</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1759265273332149</v>
+        <v>0.1322389272937246</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.343018538516064</v>
+        <v>-1.391395808018986</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.152252589157484</v>
+        <v>2.123226227455731</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.831160766733268</v>
+        <v>-6.940379766831994</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2227410752706445</v>
+        <v>0.1790534752311537</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.219727403698933</v>
+        <v>-1.268104673201856</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.223725364058339</v>
+        <v>2.194699002356586</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.810011567829824</v>
+        <v>-6.919230567928551</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2389017330693468</v>
+        <v>0.195214133029856</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.19857820479549</v>
+        <v>-1.246955474298412</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.24411586163773</v>
+        <v>2.215089499935977</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788097</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.56624612584638</v>
+        <v>-6.675465125945107</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3321886182097753</v>
+        <v>0.2885010181702845</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.19857820479549</v>
+        <v>-1.246955474298412</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.239896569984781</v>
+        <v>2.210870208283028</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527529</v>
+        <v>3.824307657527528</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.41934909812851</v>
+        <v>-6.528568098227236</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3930717432169391</v>
+        <v>0.3493841431774487</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.150919962816902</v>
+        <v>-1.199297232319824</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.27061582909195</v>
+        <v>2.241589467390196</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.169498704179436</v>
+        <v>-6.278717704278161</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4857539757802711</v>
+        <v>0.4420663757407808</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.150919962816902</v>
+        <v>-1.199297232319824</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.263357904075652</v>
+        <v>2.234331542373898</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359544114815</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.993606611712003</v>
+        <v>-6.102825611810729</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5597099362878928</v>
+        <v>0.5160223362484024</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.150919962816902</v>
+        <v>-1.199297232319824</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.266957027596301</v>
+        <v>2.237930665894547</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862989</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.82216014868954</v>
+        <v>-5.931379148788266</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6416160275514318</v>
+        <v>0.5979284275119414</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9794734997944387</v>
+        <v>-1.027850769297361</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.383152411464332</v>
+        <v>2.354126049762579</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102783</v>
+        <v>3.77376164710278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.597127149020717</v>
+        <v>-5.706346149119443</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7306497050352578</v>
+        <v>0.6869621049957675</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7544405001256158</v>
+        <v>-0.8028177696285385</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.517192688881923</v>
+        <v>2.488166327180169</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353076</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.533491406786783</v>
+        <v>-5.642710406885509</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7607988029831492</v>
+        <v>0.7171112029436588</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6908047578916813</v>
+        <v>-0.7391820273946039</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.560068935276601</v>
+        <v>2.531042573574847</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.79881119554478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.440491365580884</v>
+        <v>-5.54971036567961</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7791930782493042</v>
+        <v>0.7355054782098138</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6908047578916813</v>
+        <v>-0.7391820273946039</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.541263194060396</v>
+        <v>2.512236832358643</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712295</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.200060868776024</v>
+        <v>-5.30927986887475</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8771083535961255</v>
+        <v>0.8334207535566351</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.450374261086821</v>
+        <v>-0.4987515305897436</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.68726456876819</v>
+        <v>2.658238207066436</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837686</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.127818300604829</v>
+        <v>-5.237037300703555</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9099346946994236</v>
+        <v>0.8662470946599332</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.450374261086821</v>
+        <v>-0.4987515305897436</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.69119388260301</v>
+        <v>2.662167520901257</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.074819978323442</v>
+        <v>-5.184038978422167</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9318126075293187</v>
+        <v>0.8881250074898284</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3950380020848822</v>
+        <v>-0.4434152715878048</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.725074221921513</v>
+        <v>2.69604786021976</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.966015092843715</v>
+        <v>-5.098148611699036</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.972332632941203</v>
+        <v>0.9194792253990745</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3950380020848822</v>
+        <v>-0.4434152715878048</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.722072293141507</v>
+        <v>2.693045931439753</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866537614594</v>
+        <v>3.818665376145935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.745994294806704</v>
+        <v>-4.878127813662025</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.061919989166621</v>
+        <v>1.009066581624493</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2538181570169019</v>
+        <v>-0.3021954265198246</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.808383237192909</v>
+        <v>2.779356875491156</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009952</v>
+        <v>3.843270952009948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.613126605743426</v>
+        <v>-4.745260124598747</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.130961247593756</v>
+        <v>1.078107840051627</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2538181570169019</v>
+        <v>-0.3021954265198246</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.824277419994733</v>
+        <v>2.795251058292979</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966261</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.453611502224057</v>
+        <v>-4.585745021079378</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.195913133441806</v>
+        <v>1.143059725899677</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.09430305349753199</v>
+        <v>-0.1426803230004546</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.921132326546656</v>
+        <v>2.892105964844903</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046999</v>
+        <v>3.791269976046998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.308939357124319</v>
+        <v>-4.44107287597964</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.26387009404314</v>
+        <v>1.211016686501012</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.05036909160220543</v>
+        <v>0.001991822099282781</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.018023716167939</v>
+        <v>2.988997354466185</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412107</v>
+        <v>3.735835647412106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.368814184482011</v>
+        <v>-4.500947703337332</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.225957654501489</v>
+        <v>1.173104246959361</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.009505735755486688</v>
+        <v>-0.05788300525840934</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.968136311154749</v>
+        <v>2.939109949452996</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144519</v>
+        <v>3.762643902144518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.423069227337614</v>
+        <v>-4.414148205558323</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.226656130681814</v>
+        <v>1.230224539393531</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.009505735755486688</v>
+        <v>-0.05788300525840934</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.990536804477316</v>
+        <v>2.961510442775562</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900696</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.42553893379942</v>
+        <v>-4.416617912020129</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.225740649470504</v>
+        <v>1.22930905818222</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.01197544221729285</v>
+        <v>-0.0603527117202155</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.989127381973644</v>
+        <v>2.96010102027189</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473602</v>
+        <v>3.743216620473599</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.49390912012343</v>
+        <v>-4.484988098344139</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.209399497415602</v>
+        <v>1.212967906127318</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.002699743181077907</v>
+        <v>-0.05107701268400056</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.005699723870075</v>
+        <v>2.976673362168321</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978371</v>
+        <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.602447301039564</v>
+        <v>-4.593526279260273</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.15642093368104</v>
+        <v>1.159989342392756</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.002699743181077907</v>
+        <v>-0.05107701268400056</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.996136432501966</v>
+        <v>2.967110070800213</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887705</v>
+        <v>3.7109031558877</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.633440460368269</v>
+        <v>-4.624519438588979</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9687332349899447</v>
+        <v>0.9723016437016607</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.002699743181077907</v>
+        <v>-0.05107701268400056</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.820845997542353</v>
+        <v>2.7918196358406</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675901</v>
+        <v>3.746038950675895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.4579662005758</v>
+        <v>-4.44904517879651</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.04349017089872</v>
+        <v>1.047058579610436</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.002699743181077907</v>
+        <v>-0.05107701268400056</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.825413229534141</v>
+        <v>2.796386867832387</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695446</v>
+        <v>3.765020747695441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.568902453217049</v>
+        <v>-4.559981431437759</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9748576986034274</v>
+        <v>0.9784261073151435</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.002699743181077907</v>
+        <v>-0.05107701268400056</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.801155258295348</v>
+        <v>2.772128896593594</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581293</v>
+        <v>3.773206721581292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.771929030760282</v>
+        <v>-4.763008008980992</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8967784528060396</v>
+        <v>0.9003468615177557</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2057263207243113</v>
+        <v>-0.2541035902272339</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.682470696989313</v>
+        <v>2.65344433528756</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.614003431824989</v>
+        <v>-4.605082410045699</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9701210788122892</v>
+        <v>0.9736894875240054</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2057263207243113</v>
+        <v>-0.2541035902272339</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.692643083421446</v>
+        <v>2.663616721719692</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212298</v>
+        <v>3.786946382212297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.527759968798612</v>
+        <v>-4.518838947019321</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9995647345967007</v>
+        <v>1.003133143308417</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2057263207243113</v>
+        <v>-0.2541035902272339</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.687589353995306</v>
+        <v>2.658562992293553</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786045</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.528943053449673</v>
+        <v>-4.520022031670383</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9908672761808015</v>
+        <v>0.9944356848925178</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2113693691908228</v>
+        <v>-0.2597466386937455</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.675979300359925</v>
+        <v>2.646952938658171</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.40581534645559</v>
+        <v>-4.3968943246763</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.040670232011536</v>
+        <v>1.044238640723252</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2113693691908228</v>
+        <v>-0.2597466386937455</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.676531173393026</v>
+        <v>2.647504811691272</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279501</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.443617851073695</v>
+        <v>-4.30408384322544</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9548219220556602</v>
+        <v>1.010635525194962</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2491718738089274</v>
+        <v>-0.1669361572428861</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.583122362513529</v>
+        <v>2.632463792453154</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030428</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.395054798852665</v>
+        <v>-4.25552079100441</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9761206188686729</v>
+        <v>1.031934222007975</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2006088215878972</v>
+        <v>-0.1183731050218559</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.614133669770748</v>
+        <v>2.663475099710373</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.282383580616415</v>
+        <v>-4.14284957276816</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.016264814674896</v>
+        <v>1.072078417814198</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.08793760335164696</v>
+        <v>-0.005701886785605736</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.676812109224221</v>
+        <v>2.726153539163846</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.340983121941723</v>
+        <v>-4.030472571585487</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.99831629397544</v>
+        <v>1.122520514117934</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.08793760335164696</v>
+        <v>-0.005701886785605736</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.682303405054888</v>
+        <v>2.731644834994513</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968865</v>
+        <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.437278743000276</v>
+        <v>-4.228707140472218</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9712952473205578</v>
+        <v>1.054723888331781</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1842332244101994</v>
+        <v>-0.2039364556723363</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.636023234188296</v>
+        <v>2.624201295431014</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175325</v>
+        <v>3.643066046175322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.520280024025555</v>
+        <v>-4.311708421497497</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7764504549110995</v>
+        <v>0.8598790959223228</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2028041089373732</v>
+        <v>-0.2225073401995101</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.463236423472645</v>
+        <v>2.451414484715363</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271273519927</v>
+        <v>3.682712735199266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.647347030332543</v>
+        <v>-4.438775427804485</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.84577331310751</v>
+        <v>0.9292019541187331</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2028041089373732</v>
+        <v>-0.2225073401995101</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.583386084191851</v>
+        <v>2.571564145434569</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73300886566077</v>
+        <v>3.733008865660765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.733945613313645</v>
+        <v>-4.525374010785588</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8256469060173919</v>
+        <v>0.9090755470286149</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2028041089373732</v>
+        <v>-0.2225073401995101</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.597899110294174</v>
+        <v>2.586077171536892</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383425</v>
+        <v>3.741170494383421</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.695561950755494</v>
+        <v>-4.486990348227437</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8384198123830209</v>
+        <v>0.9218484533942441</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.164420446379222</v>
+        <v>-0.1841236776413589</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.618348749171433</v>
+        <v>2.606526810414151</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002486</v>
+        <v>3.751143622002481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.518445620720328</v>
+        <v>-4.309874018192271</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9059953732423893</v>
+        <v>0.9894240142536124</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.164420446379222</v>
+        <v>-0.1841236776413589</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.615077778016735</v>
+        <v>2.603255839259453</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263903</v>
+        <v>3.741324873263898</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.488743496744035</v>
+        <v>-4.280171894215977</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9185596145948198</v>
+        <v>1.001988255606043</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1688905715945354</v>
+        <v>-0.1885938028566723</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.61307909464946</v>
+        <v>2.601257155892178</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481236</v>
+        <v>3.750725801481231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.309368075505267</v>
+        <v>-4.100796472977209</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9840967583967413</v>
+        <v>1.067525399407964</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.01211381342381668</v>
+        <v>-0.03181704468595359</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.700932124858306</v>
+        <v>2.689110186101023</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71698814345223</v>
+        <v>3.716988143452227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.354382289025873</v>
+        <v>-4.145810686497816</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9468985283200888</v>
+        <v>1.030327169331311</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.04246270873842128</v>
+        <v>-0.0621659400005582</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.663530243001133</v>
+        <v>2.65170830424385</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979538</v>
+        <v>3.737023032979534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.621386799298308</v>
+        <v>-4.412815196770251</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8457882865500606</v>
+        <v>0.9292169275612832</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2368257467813699</v>
+        <v>-0.2565289780435068</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.552603982514309</v>
+        <v>2.540782043757027</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.72258458073548</v>
+        <v>-4.514012978207424</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8045130958716928</v>
+        <v>0.8879417368829157</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3052345603266891</v>
+        <v>-0.324937791588826</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.510762616283619</v>
+        <v>2.498940677526337</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.690108994564708</v>
+        <v>-4.481537392036651</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8151032918943184</v>
+        <v>0.8985319329055412</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3052345603266891</v>
+        <v>-0.324937791588826</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.508362577837936</v>
+        <v>2.496540639080654</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.671070866857411</v>
+        <v>-4.462499264329354</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8192432621854824</v>
+        <v>0.902671903196705</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3634181716578836</v>
+        <v>-0.3831214029200205</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.469977130247464</v>
+        <v>2.458155191490182</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601254</v>
+        <v>3.731060897601253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.702197498008029</v>
+        <v>-4.493625895479973</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9843744786639155</v>
+        <v>1.067803119675138</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3634181716578836</v>
+        <v>-0.3831214029200205</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.647558999186145</v>
+        <v>2.635737060428863</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537867</v>
+        <v>3.722443786537864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.754517878608821</v>
+        <v>-4.545946276080764</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9642796554097324</v>
+        <v>1.047708296420955</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3284713116490114</v>
+        <v>-0.3481745429111484</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.669360444177602</v>
+        <v>2.657538505420319</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259124</v>
+        <v>3.787422005259121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.89884078453374</v>
+        <v>-4.690269182005683</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9125590234366907</v>
+        <v>0.9959876644479135</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3284713116490114</v>
+        <v>-0.3481745429111484</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.675368974574527</v>
+        <v>2.663547035817245</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78149767498991</v>
+        <v>3.781497674989905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.751097814298737</v>
+        <v>-4.542526211770681</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.050808859322714</v>
+        <v>1.134237500333936</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1606639544141283</v>
+        <v>-0.1803671856762652</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.855206036707479</v>
+        <v>2.843384097950197</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651172</v>
+        <v>3.802242353651167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.853112496829959</v>
+        <v>-4.644540894301902</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.012796607841706</v>
+        <v>1.096225248852929</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1606639544141283</v>
+        <v>-0.1803671856762652</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.85799965823896</v>
+        <v>2.846177719481678</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864731</v>
+        <v>3.805605409864727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.716503152735866</v>
+        <v>-4.507931550207809</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.068102693871002</v>
+        <v>1.151531334882224</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.02405461032003581</v>
+        <v>-0.04375784158217272</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.940627613087074</v>
+        <v>2.928805674329792</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360614</v>
+        <v>3.798236219360613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.859268485558516</v>
+        <v>-4.650696883030459</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.010077037482052</v>
+        <v>1.093505678493274</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1668199431426862</v>
+        <v>-0.1865231744048231</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.854048890133594</v>
+        <v>2.842226951376312</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268427</v>
+        <v>3.867359061268424</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.796970486782394</v>
+        <v>-4.588398884254337</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.101331790789322</v>
+        <v>1.184760431800544</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1668199431426862</v>
+        <v>-0.1865231744048231</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.920384443930415</v>
+        <v>2.908562505173133</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462193</v>
+        <v>3.848725564462187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.793258395382968</v>
+        <v>-4.386608686589179</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8113974997384901</v>
+        <v>0.9740573832560055</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1611996183602881</v>
+        <v>0.01149501776433126</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.632337511189252</v>
+        <v>2.735954292864023</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841441242322422</v>
+        <v>3.841441242322421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.7993475145276</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.733367713740375</v>
+        <v>-4.326718004946586</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9056440047177026</v>
+        <v>1.068303888235218</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.1013089367176946</v>
+        <v>0.07138569940692474</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.738562152496983</v>
+        <v>2.842178934171755</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819059724789549</v>
+        <v>3.819059724789543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.813975250643643</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.831108258365349</v>
+        <v>-4.42445854957156</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8811755229837563</v>
+        <v>1.043835406501272</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1171982148506748</v>
+        <v>0.05549642127394455</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.743656321733239</v>
+        <v>2.84727310340801</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831815456959392</v>
+        <v>3.831815456959383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.812511231468315</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.007446018488278</v>
+        <v>-4.430610188429458</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8091763997592563</v>
+        <v>1.039910731782784</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2935359749736042</v>
+        <v>0.04934478241604651</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.636389646484153</v>
+        <v>2.842118100917943</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.44008805540053</v>
+        <v>3.89456553753201</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.54459412704105</v>
+        <v>2.946529248364446</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.007446018488278</v>
+        <v>-4.430610188429458</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8091763997592563</v>
+        <v>1.039910731782784</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2935359749736042</v>
+        <v>0.04934478241604651</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.537657924027418</v>
+        <v>2.939593045350814</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240525.xlsx
+++ b/tame_output/ON/bt/strategyON_20240525.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>342</v>
+        <v>394</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>83.2%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,40 +786,40 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-23.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-51.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.1%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-665.4%</t>
+          <t>-518.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,47 +992,47 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.0%</t>
+          <t>439.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-20.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-604.6%</t>
+          <t>-374.4%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,22 +1102,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1131,66 +1131,66 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.5%</t>
+          <t>-205.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-272.2%</t>
+          <t>-172.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1289,31 +1289,31 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-292.6%</t>
+          <t>-248.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>-187.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-219.1%</t>
+          <t>-228.0%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,31 +1447,31 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-175.9%</t>
+          <t>-146.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-152.1%</t>
+          <t>-159.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1975"/>
+  <dimension ref="A1:G1974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386097</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998565</v>
+        <v>3.367370539998564</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082129</v>
+        <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757927</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153011</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382195</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.565657023012474</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.711471304233509</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2413167039278764</v>
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1856" t="n">
-        <v>3.139859661206862</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.909339796239137</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.57576731839746</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3492227559550946</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.930326007633806</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1857" t="n">
-        <v>3.13596571986312</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.115851573126158</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.489268666298909</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.555734532842116</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.802525000157851</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1858" t="n">
-        <v>3.137738646563379</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.371692658904851</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.388705158687692</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.555734532842116</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.80429792685811</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1859" t="n">
-        <v>3.124071534030784</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.803498452054638</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.202315728895181</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.692152029283383</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.708780316460754</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1860" t="n">
-        <v>3.112356309032875</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.038192446187191</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.096722906244251</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6858157620541279</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.700866851800398</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1861" t="n">
-        <v>3.11093690068884</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.373855093417643</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9610384390080351</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6858157620541279</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.699447443456363</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1862" t="n">
-        <v>3.117424460923081</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.737481338317957</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8220755012821512</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7840373989212537</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.647002021570329</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1863" t="n">
-        <v>3.116678975928913</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.102608720956703</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6752790632324839</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.080348183220266</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.468470065996753</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.115440519943672</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.511197498137381</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.510605096374972</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.488936960400945</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.222078343703105</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.110625952415132</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.848615329049017</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3708233964817782</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.488936960400945</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.217263776174566</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.10862000302401</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.265007203336014</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2022606973758565</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.488936960400945</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.215257826783443</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.118878693692689</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.581619145876663</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.08587461102827643</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.488936960400945</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.225516517452122</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.114978258838384</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.927493967861471</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.05637575261995176</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.488936960400945</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.221616082597818</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.113383178893385</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.091073846045855</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1234027838387046</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.488936960400945</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.220021002652818</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.117162154822593</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.387735187856054</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2382883446335757</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.557680096134823</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.182554097141699</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.11313585028819</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.59276636863037</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3243271214777055</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.557680096134823</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.178527792607296</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.113033748966606</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.975767757373001</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4776297782963419</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.557680096134823</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.178425691285712</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.115605264938036</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.157637548358036</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5478061787189259</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.739549887119858</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.071875332666121</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.120955568236086</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.517167870862037</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6862680044224763</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.739549887119858</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.077225635964171</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.128871588193264</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.567516934316259</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6984916098469873</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.78989895057408</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.054932217848815</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776674</v>
+        <v>3.925690004306867</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.131913338815032</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.665136211737655</v>
+        <v>-3.565157061035161</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7344975701937773</v>
+        <v>1.711671289024434</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.887518227995477</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.999402402017747</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.685768606310301</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.131913338815032</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.661445286781245</v>
+        <v>-3.561466136078749</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7330212002112129</v>
+        <v>1.713147659006999</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.887518227995477</v>
+        <v>-0.2413167039278764</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.999402402017747</v>
+        <v>2.993300515395521</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.696110293514505</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.137426535933675</v>
+        <v>3.143603734870888</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.865703462111108</v>
+        <v>-3.765724311408613</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8092112732245158</v>
+        <v>1.636957585993696</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.015157172609466</v>
+        <v>-0.3689556485418652</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.928332232367996</v>
+        <v>2.922230345745769</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.690171799102695</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.141909090418111</v>
+        <v>3.148086289355324</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.0075132363179</v>
+        <v>-3.9075340856154</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.861452628422795</v>
+        <v>1.584716230795417</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.186435970255041</v>
+        <v>-0.5402344461874405</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.830047508265086</v>
+        <v>2.82394562164286</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.693291633813439</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.157280791911532</v>
+        <v>3.163457990848745</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.934043404650447</v>
+        <v>-3.834064253947952</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8166929942623944</v>
+        <v>1.629475864955817</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.112966138587593</v>
+        <v>-0.4667646145199921</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.889501108758977</v>
+        <v>2.883399222136751</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.683379135981407</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.171836012659049</v>
+        <v>3.178013211596262</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.10916782203699</v>
+        <v>-4.009188671334496</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8721875404694952</v>
+        <v>1.573981318748717</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.288090555974136</v>
+        <v>-0.641889031906536</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.798981679074567</v>
+        <v>2.792879792452341</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.67919848878308</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.164616847757453</v>
+        <v>3.170794046694666</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.34361991605148</v>
+        <v>-4.243640765348986</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9731875429768864</v>
+        <v>1.472981316241325</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.288090555974136</v>
+        <v>-0.641889031906536</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.791762514172971</v>
+        <v>2.785660627550745</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.674012387137205</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.157944656983477</v>
+        <v>3.16412185592069</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.63142376058872</v>
+        <v>-4.531444609886224</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.094981271565759</v>
+        <v>1.351187587652453</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.575894400511375</v>
+        <v>-0.9296928764437741</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.612408016676652</v>
+        <v>2.606306130054426</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.687035908763395</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.159060446822033</v>
+        <v>3.165237645759246</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.68420991618905</v>
+        <v>-4.58423076548655</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.114979943967333</v>
+        <v>1.331188915250879</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.671569887093772</v>
+        <v>-1.025368363026171</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.55611851456577</v>
+        <v>2.550016627943544</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.685421535670209</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.161754175451148</v>
+        <v>3.167931374388361</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.91623883592531</v>
+        <v>-4.816259685222811</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.205097783232723</v>
+        <v>1.241071075985489</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.733582584282195</v>
+        <v>-1.087381060214594</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.521604624881831</v>
+        <v>2.515502738259605</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.766993919695353</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.165744511137548</v>
+        <v>3.171921710074762</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.86422332195649</v>
+        <v>-4.764244171253999</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.180301241958797</v>
+        <v>1.265867617259415</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.733582584282195</v>
+        <v>-1.087381060214594</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.525594960568232</v>
+        <v>2.519493073946006</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.793358159531731</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.164269284238807</v>
+        <v>3.17044648317602</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.00589516368061</v>
+        <v>-4.90591601297812</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.238445205547187</v>
+        <v>1.207723653671025</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.733582584282195</v>
+        <v>-1.087381060214594</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.52411973366949</v>
+        <v>2.518017847047264</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.884891628313525</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.179322694403679</v>
+        <v>3.185499893340892</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.95630431925578</v>
+        <v>-4.856325168553286</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.20355545761238</v>
+        <v>1.242613401605831</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.683991739857361</v>
+        <v>-1.03779021578976</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.568927650489263</v>
+        <v>2.562825763867036</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.870161444143385</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.166271560756996</v>
+        <v>3.172448759694209</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.75715221201868</v>
+        <v>-4.657173061316187</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.136945748364224</v>
+        <v>1.309223110853987</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.518669213907548</v>
+        <v>-0.8724676898399472</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.655070032412468</v>
+        <v>2.648968145790241</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.878481275988087</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.175850633793205</v>
+        <v>3.182027832730418</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.53130705929927</v>
+        <v>-4.431327908596776</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.037028614240251</v>
+        <v>1.40914024497796</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.476742538320384</v>
+        <v>-0.8305410142527835</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.689805110800975</v>
+        <v>2.683703224178748</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.832339160005338</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.176989778349264</v>
+        <v>3.183166977286477</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.40672840296168</v>
+        <v>-4.316111455041868</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9860580071491545</v>
+        <v>1.456365970955983</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.476742538320384</v>
+        <v>-0.8305410142527835</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.690944255357034</v>
+        <v>2.684842368734807</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.832339160005338</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.179623552511371</v>
+        <v>3.183166977286477</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.45962369100596</v>
+        <v>-4.316111455041868</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.004582348204762</v>
+        <v>1.456365970955983</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.471787192231938</v>
+        <v>-0.8305410142527835</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.696551237172209</v>
+        <v>2.684842368734807</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.832339160005338</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.185357256750008</v>
+        <v>3.183166977286477</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.17571496007722</v>
+        <v>-4.316111455041868</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8852851515946254</v>
+        <v>1.456365970955983</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.471787192231938</v>
+        <v>-0.8305410142527835</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.702284941410845</v>
+        <v>2.684842368734807</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.832339160005338</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.175619994356143</v>
+        <v>3.183166977286477</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.15272583697049</v>
+        <v>-4.316111455041868</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8858267647458016</v>
+        <v>1.456365970955983</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.448798069125213</v>
+        <v>-0.8305410142527835</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.706341152881015</v>
+        <v>2.684842368734807</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.832339160005338</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.165736513043235</v>
+        <v>3.183166977286477</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.888888969766422</v>
+        <v>-4.316111455041868</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7901754991770811</v>
+        <v>1.456365970955983</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.448798069125213</v>
+        <v>-0.8305410142527835</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.696457671568107</v>
+        <v>2.684842368734807</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.832339160005338</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.163901952543861</v>
+        <v>3.183166977286477</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.621647168898024</v>
+        <v>-4.316111455041868</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6851133393290958</v>
+        <v>1.456365970955983</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.448798069125213</v>
+        <v>-0.8305410142527835</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.694623111068734</v>
+        <v>2.684842368734807</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.832339160005338</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.1636016375704</v>
+        <v>3.183166977286477</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.523740130221533</v>
+        <v>-4.316111455041868</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6462508388319601</v>
+        <v>1.456365970955983</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.380812319264657</v>
+        <v>-0.8305410142527835</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.735114246011607</v>
+        <v>2.684842368734807</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567238</v>
+        <v>3.832339160005338</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.164270143715894</v>
+        <v>3.183166977286477</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.499786589245575</v>
+        <v>-4.316111455041868</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6360009162960836</v>
+        <v>1.456365970955983</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.356858778288699</v>
+        <v>-0.8305410142527835</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.750154876742675</v>
+        <v>2.684842368734807</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487767</v>
+        <v>3.832339160005338</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.151009827554142</v>
+        <v>3.183166977286477</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.235726650922778</v>
+        <v>-4.316111455041868</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5436372571287169</v>
+        <v>1.456365970955983</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.092798839965903</v>
+        <v>-0.8305410142527835</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.895330523574601</v>
+        <v>2.684842368734807</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.832339160005338</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.148222793893841</v>
+        <v>3.183166977286477</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.528647027417941</v>
+        <v>-4.316111455041868</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2635924413870829</v>
+        <v>1.456365970955983</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.092798839965903</v>
+        <v>-0.8305410142527835</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.8925434899143</v>
+        <v>2.684842368734807</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.832339160005338</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.148566417781682</v>
+        <v>3.183166977286477</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.488462729051751</v>
+        <v>-4.316111455041868</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2471750981527654</v>
+        <v>1.456365970955983</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.052614541599712</v>
+        <v>-0.8305410142527835</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.916997692821855</v>
+        <v>2.684842368734807</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096471</v>
+        <v>3.832339160005338</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.147933239002439</v>
+        <v>3.183166977286477</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.408392933513946</v>
+        <v>-4.316111455041868</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2157803587168865</v>
+        <v>1.456365970955983</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.972544746061908</v>
+        <v>-0.8305410142527835</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.964406391365295</v>
+        <v>2.684842368734807</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.985288251388841</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.155857667840292</v>
+        <v>3.183166977286477</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.174911711284349</v>
+        <v>-4.304845061268599</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.114463440987195</v>
+        <v>1.46087252846529</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.739063523832309</v>
+        <v>-0.8305410142527835</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.112419553540906</v>
+        <v>2.684842368734807</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255787</v>
+        <v>3.999594944882818</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.152965457527332</v>
+        <v>3.180274766973518</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.025245320276834</v>
+        <v>-4.155178670261084</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.05748909489714871</v>
+        <v>1.517846874555337</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.646160032589773</v>
+        <v>-0.7376375230102475</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.165269437973468</v>
+        <v>2.73769225316737</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76317867286043</v>
+        <v>3.961140070487461</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.14833294427436</v>
+        <v>3.175642253720545</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.892969846645948</v>
+        <v>-4.022903196630198</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.009211418697767204</v>
+        <v>1.566124550754719</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.513884558958887</v>
+        <v>-0.6053620493793609</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.240002208899028</v>
+        <v>2.812425024092929</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.982676616202987</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.151148004961996</v>
+        <v>3.178457314408182</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.702370171972795</v>
+        <v>-3.832303521957045</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.06984351185913074</v>
+        <v>1.645179481311616</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.323284884285734</v>
+        <v>-0.414762374706208</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.357177074390556</v>
+        <v>2.929599889584457</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75387899643099</v>
+        <v>3.951840394058022</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.164054346185655</v>
+        <v>3.19136365563184</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.453370373289214</v>
+        <v>-3.583303723273465</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.182349772556222</v>
+        <v>1.757685742008707</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.323284884285734</v>
+        <v>-0.414762374706208</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.370083415614215</v>
+        <v>2.942506230808116</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.890889677704678</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.036078416586436</v>
+        <v>3.063387726032621</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.558960363062319</v>
+        <v>-3.688893713046569</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.01213784704776133</v>
+        <v>1.587473816500246</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.428874874058838</v>
+        <v>-0.5203523644793124</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.178753492151134</v>
+        <v>2.751176307345034</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.968380406084933</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.084622758463523</v>
+        <v>3.111932067909708</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.577695265180916</v>
+        <v>-3.707628615165166</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.05318822807740897</v>
+        <v>1.628524197529894</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.428874874058838</v>
+        <v>-0.5203523644793124</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.22729783402822</v>
+        <v>2.79972064922212</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.958291508807842</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.964743835775355</v>
+        <v>2.99205314522154</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.429755223773316</v>
+        <v>-3.559688573757567</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.007514678047718881</v>
+        <v>1.567821291404766</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.408553958150281</v>
+        <v>-0.5000314485707549</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.119611460885187</v>
+        <v>2.692034276079087</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.921524051506236</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.956029849521877</v>
+        <v>2.983339158968062</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.412597073642022</v>
+        <v>-3.542530423626272</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.009365404248679265</v>
+        <v>1.565970565203806</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.391395808018986</v>
+        <v>-0.4828732984394606</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.121192364710486</v>
+        <v>2.693615179904386</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996614056811</v>
+        <v>3.927927538195142</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.949069237426784</v>
+        <v>2.976378546872969</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.369048666871332</v>
+        <v>-3.498982016855582</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.001093346364503756</v>
+        <v>1.576429315816989</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.391395808018986</v>
+        <v>-0.4828732984394606</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.114231752615392</v>
+        <v>2.686654567809293</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963421</v>
+        <v>3.980880355590454</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.963531591807927</v>
+        <v>2.990840901254112</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.126900273417474</v>
+        <v>-3.256833623401724</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1124150581271901</v>
+        <v>1.687751027579675</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.391395808018986</v>
+        <v>-0.4828732984394606</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.128694106996535</v>
+        <v>2.701116922190436</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192819</v>
+        <v>4.026509308819852</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.958063712267122</v>
+        <v>2.985373021713307</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.063670901649125</v>
+        <v>-3.193604251633376</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1322389272937246</v>
+        <v>1.707574896746209</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.391395808018986</v>
+        <v>-0.4828732984394606</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.123226227455731</v>
+        <v>2.695649042649631</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>4.026010750889082</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.955561806277699</v>
+        <v>2.982871115723884</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.940379766831994</v>
+        <v>-3.070313116816245</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1790534752311537</v>
+        <v>1.754389444683638</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.268104673201856</v>
+        <v>-0.3595821636223301</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.194699002356586</v>
+        <v>2.767121817550486</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389912</v>
+        <v>4.010411501016945</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.963262784515024</v>
+        <v>2.990572093961209</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.919230567928551</v>
+        <v>-3.049163917912802</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.195214133029856</v>
+        <v>1.770550102482341</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.246955474298412</v>
+        <v>-0.3384329647188868</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.215089499935977</v>
+        <v>2.787512315129877</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.946286230415129</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.959043492862075</v>
+        <v>2.98635280230826</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.675465125945107</v>
+        <v>-2.805398475929358</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2885010181702845</v>
+        <v>1.863836987622769</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.246955474298412</v>
+        <v>-0.3384329647188868</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.210870208283028</v>
+        <v>2.783293023476928</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527528</v>
+        <v>4.02226905515456</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.961167806782091</v>
+        <v>2.988477116228275</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.528568098227236</v>
+        <v>-2.658501448211487</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3493841431774487</v>
+        <v>1.924720112629934</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.199297232319824</v>
+        <v>-0.2907747227402988</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.241589467390196</v>
+        <v>2.814012282584097</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>4.024312796376217</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.953909881765793</v>
+        <v>2.981219191211978</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.278717704278161</v>
+        <v>-2.408651054262413</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4420663757407808</v>
+        <v>2.017402345193265</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.199297232319824</v>
+        <v>-0.2907747227402988</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.234331542373898</v>
+        <v>2.806754357567799</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>4.033915809108529</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.957509005286441</v>
+        <v>2.984818314732626</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.102825611810729</v>
+        <v>-2.23275896179498</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5160223362484024</v>
+        <v>2.091358305700887</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.199297232319824</v>
+        <v>-0.2907747227402988</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.237930665894547</v>
+        <v>2.810353481088447</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.860755523105283</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.970836511340995</v>
+        <v>2.99814582078718</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.931379148788266</v>
+        <v>-2.073664045121362</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5979284275119414</v>
+        <v>2.168323778424888</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.027850769297361</v>
+        <v>-0.1316798060666801</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.354126049762579</v>
+        <v>2.919137937147172</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376164710278</v>
+        <v>3.860755523105283</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.969856988957292</v>
+        <v>2.99814582078718</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.706346149119443</v>
+        <v>-2.073664045121362</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6869621049957675</v>
+        <v>2.168323778424888</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8028177696285385</v>
+        <v>-0.1316798060666801</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.488166327180169</v>
+        <v>2.919137937147172</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.860755523105283</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.974551790011609</v>
+        <v>2.99814582078718</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.642710406885509</v>
+        <v>-2.073664045121362</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7171112029436588</v>
+        <v>2.168323778424888</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7391820273946039</v>
+        <v>-0.1316798060666801</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.531042573574847</v>
+        <v>2.919137937147172</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881119554478</v>
+        <v>3.860755523105283</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.955746048795405</v>
+        <v>2.99814582078718</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.54971036567961</v>
+        <v>-2.073664045121362</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7355054782098138</v>
+        <v>2.168323778424888</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7391820273946039</v>
+        <v>-0.1316798060666801</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.512236832358643</v>
+        <v>2.919137937147172</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.860755523105283</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.957489125420282</v>
+        <v>2.99814582078718</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.30927986887475</v>
+        <v>-2.073664045121362</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8334207535566351</v>
+        <v>2.168323778424888</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4987515305897436</v>
+        <v>-0.1316798060666801</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.658238207066436</v>
+        <v>2.919137937147172</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.860755523105283</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.961418439255103</v>
+        <v>2.99814582078718</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.237037300703555</v>
+        <v>-2.073664045121362</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8662470946599332</v>
+        <v>2.168323778424888</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4987515305897436</v>
+        <v>-0.1316798060666801</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.662167520901257</v>
+        <v>2.919137937147172</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.860755523105283</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.962097023172443</v>
+        <v>2.99814582078718</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.184038978422167</v>
+        <v>-2.073664045121362</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8881250074898284</v>
+        <v>2.168323778424888</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4434152715878048</v>
+        <v>-0.1316798060666801</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.69604786021976</v>
+        <v>2.919137937147172</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972336</v>
+        <v>3.860755523105283</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.959095094392436</v>
+        <v>2.99814582078718</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.098148611699036</v>
+        <v>-2.073664045121362</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9194792253990745</v>
+        <v>2.168323778424888</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4434152715878048</v>
+        <v>-0.1316798060666801</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.693045931439753</v>
+        <v>2.919137937147172</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145935</v>
+        <v>3.860755523105283</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.96067413140305</v>
+        <v>2.99814582078718</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.878127813662025</v>
+        <v>-2.073664045121362</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.009066581624493</v>
+        <v>2.168323778424888</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3021954265198246</v>
+        <v>-0.1316798060666801</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.779356875491156</v>
+        <v>2.919137937147172</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009948</v>
+        <v>3.860755523105283</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.976568314204874</v>
+        <v>2.99814582078718</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.745260124598747</v>
+        <v>-2.073664045121362</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.078107840051627</v>
+        <v>2.168323778424888</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3021954265198246</v>
+        <v>-0.1316798060666801</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.795251058292979</v>
+        <v>2.919137937147172</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>4.076849183395007</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.977714158645175</v>
+        <v>2.99814582078718</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.585745021079378</v>
+        <v>-2.079691069651433</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.143059725899677</v>
+        <v>2.165912968612859</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1426803230004546</v>
+        <v>-0.1316798060666801</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.892105964844903</v>
+        <v>2.919137937147172</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046998</v>
+        <v>4.023075348475745</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.987802261206615</v>
+        <v>3.00823392334862</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.44107287597964</v>
+        <v>-1.935018924551696</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.211016686501012</v>
+        <v>2.233869929214194</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.001991822099282781</v>
+        <v>0.0129923390330573</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.988997354466185</v>
+        <v>3.016029326768455</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412106</v>
+        <v>3.967641019840853</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.973839752608041</v>
+        <v>2.994271414750046</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.500947703337332</v>
+        <v>-1.994893751909388</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.173104246959361</v>
+        <v>2.195957489672543</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.05788300525840934</v>
+        <v>-0.04688248832463482</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.939109949452996</v>
+        <v>2.966141921755265</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144518</v>
+        <v>3.994449274573265</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.996240245930607</v>
+        <v>3.016671908072612</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.414148205558323</v>
+        <v>-1.908094254130379</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.230224539393531</v>
+        <v>2.253077782106713</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.05788300525840934</v>
+        <v>-0.04688248832463482</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.961510442775562</v>
+        <v>2.988542415077831</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.960948195329442</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.996312647304019</v>
+        <v>3.016744309446024</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.416617912020129</v>
+        <v>-1.910563960592186</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.22930905818222</v>
+        <v>2.252162300895403</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.0603527117202155</v>
+        <v>-0.04935219478644098</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.96010102027189</v>
+        <v>2.98713299257416</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473599</v>
+        <v>3.975021992902346</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.007319569778721</v>
+        <v>3.027751231920726</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.484988098344139</v>
+        <v>-1.978934146916195</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.212967906127318</v>
+        <v>2.2358211488405</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.05107701268400056</v>
+        <v>-0.04007649575022604</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.976673362168321</v>
+        <v>3.003705334470591</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>4.065275545303483</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.997756278410613</v>
+        <v>3.018187940552617</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.593526279260273</v>
+        <v>-2.087211390244628</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.159989342392756</v>
+        <v>2.182946960141019</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.05107701268400056</v>
+        <v>-0.04007649575022604</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.967110070800213</v>
+        <v>2.994142043102482</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109031558877</v>
+        <v>4.065275545303483</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.822465843450999</v>
+        <v>3.018187940552617</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.624519438588979</v>
+        <v>-2.087211390244628</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9723016437016607</v>
+        <v>2.182946960141019</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.05107701268400056</v>
+        <v>-0.04007649575022604</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.7918196358406</v>
+        <v>2.994142043102482</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675895</v>
+        <v>4.065275545303483</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.827033075442787</v>
+        <v>3.018187940552617</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.44904517879651</v>
+        <v>-2.087211390244628</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.047058579610436</v>
+        <v>2.182946960141019</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.05107701268400056</v>
+        <v>-0.04007649575022604</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.796386867832387</v>
+        <v>2.994142043102482</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695441</v>
+        <v>4.065275545303483</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.802775104203994</v>
+        <v>3.018187940552617</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.559981431437759</v>
+        <v>-2.087211390244628</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9784261073151435</v>
+        <v>2.182946960141019</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.05107701268400056</v>
+        <v>-0.04007649575022604</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.772128896593594</v>
+        <v>2.994142043102482</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581292</v>
+        <v>4.009236955567262</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.8059064894239</v>
+        <v>3.018187940552617</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.763008008980992</v>
+        <v>-2.085558974765537</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9003468615177557</v>
+        <v>2.183607926332655</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2541035902272339</v>
+        <v>-0.04007649575022604</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.65344433528756</v>
+        <v>2.994142043102482</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>4.020370610720131</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.816078875856032</v>
+        <v>3.02836032698475</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.605082410045699</v>
+        <v>-1.927633375830245</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9736894875240054</v>
+        <v>2.256950552338905</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2541035902272339</v>
+        <v>-0.04007649575022604</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.663616721719692</v>
+        <v>3.004314429534614</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212297</v>
+        <v>4.022976616198267</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.811025146429893</v>
+        <v>3.02330659755861</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.518838947019321</v>
+        <v>-1.841389912803867</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.003133143308417</v>
+        <v>2.286394208123316</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2541035902272339</v>
+        <v>-0.04007649575022604</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.658562992293553</v>
+        <v>2.999260700108475</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.988054157772015</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.802800921874418</v>
+        <v>3.015082373003136</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.520022031670383</v>
+        <v>-1.842572997454928</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9944356848925178</v>
+        <v>2.277696749707417</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2597466386937455</v>
+        <v>-0.04571954421673757</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.646952938658171</v>
+        <v>2.987650646473093</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.989597824259162</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.80335279490752</v>
+        <v>3.015634246036237</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.3968943246763</v>
+        <v>-1.879794956940722</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.044238640723252</v>
+        <v>2.263359838946201</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2597466386937455</v>
+        <v>-0.04571954421673757</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.647504811691272</v>
+        <v>2.988202519506195</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.969417259265471</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.732625486798885</v>
+        <v>2.944906937927603</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.30408384322544</v>
+        <v>-1.786984475489863</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.010635525194962</v>
+        <v>2.229756723417911</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1669361572428861</v>
+        <v>0.04709093723412178</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.632463792453154</v>
+        <v>2.973161500268076</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.984312475016399</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.734498962723486</v>
+        <v>2.946780413852204</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.25552079100441</v>
+        <v>-1.738421423268833</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.031934222007975</v>
+        <v>2.251055420230923</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1183731050218559</v>
+        <v>0.09565398945515197</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.663475099710373</v>
+        <v>3.004172807525295</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.957103853928711</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.729574671235209</v>
+        <v>2.941856122363927</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.14284957276816</v>
+        <v>-1.625750205032582</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.072078417814198</v>
+        <v>2.291199616037146</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.005701886785605736</v>
+        <v>0.2083252076914022</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.726153539163846</v>
+        <v>3.066851246978768</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.979074262254509</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.735065967065876</v>
+        <v>2.947347418194594</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.030472571585487</v>
+        <v>-1.51337320384991</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.122520514117934</v>
+        <v>2.341641712340883</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.005701886785605736</v>
+        <v>0.2083252076914022</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.731644834994513</v>
+        <v>3.072342542809436</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968862</v>
+        <v>3.925624498954833</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.746563168834415</v>
+        <v>2.958844619963133</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.228707140472218</v>
+        <v>-1.71160777273664</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.054723888331781</v>
+        <v>2.273845086554729</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2039364556723363</v>
+        <v>0.01009063880467159</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.624201295431014</v>
+        <v>2.964899003245936</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175322</v>
+        <v>3.879096280161293</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.584918888835069</v>
+        <v>2.797200339963786</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.311708421497497</v>
+        <v>-1.794609053761919</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8598790959223228</v>
+        <v>2.079000294145271</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2225073401995101</v>
+        <v>-0.008480245722502167</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.451414484715363</v>
+        <v>2.792112192530285</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199266</v>
+        <v>4.122881758883809</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.705068549554274</v>
+        <v>2.917350000682992</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.438775427804485</v>
+        <v>-1.915057255987808</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9292019541187331</v>
+        <v>2.150970673974121</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2225073401995101</v>
+        <v>-0.008480245722502167</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.571564145434569</v>
+        <v>2.912261853249491</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660765</v>
+        <v>4.122881758883809</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.719581575656597</v>
+        <v>2.917350000682992</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.525374010785588</v>
+        <v>-1.915057255987808</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9090755470286149</v>
+        <v>2.150970673974121</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2225073401995101</v>
+        <v>-0.008480245722502167</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.586077171536892</v>
+        <v>2.912261853249491</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383421</v>
+        <v>4.122881758883809</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.717001016998966</v>
+        <v>2.917350000682992</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.486990348227437</v>
+        <v>-1.915057255987808</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9218484533942441</v>
+        <v>2.150970673974121</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1841236776413589</v>
+        <v>-0.008480245722502167</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.606526810414151</v>
+        <v>2.912261853249491</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002481</v>
+        <v>4.122881758883809</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.713730045844268</v>
+        <v>2.917350000682992</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.309874018192271</v>
+        <v>-1.915057255987808</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9894240142536124</v>
+        <v>2.150970673974121</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1841236776413589</v>
+        <v>-0.008480245722502167</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.603255839259453</v>
+        <v>2.912261853249491</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263898</v>
+        <v>4.122881758883809</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.714413437606181</v>
+        <v>2.917350000682992</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.280171894215977</v>
+        <v>-1.915057255987808</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.001988255606043</v>
+        <v>2.150970673974121</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1885938028566723</v>
+        <v>-0.008480245722502167</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.601257155892178</v>
+        <v>2.912261853249491</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481231</v>
+        <v>4.122881758883809</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.708200412912595</v>
+        <v>2.917350000682992</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.100796472977209</v>
+        <v>-1.915057255987808</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.067525399407964</v>
+        <v>2.150970673974121</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.03181704468595359</v>
+        <v>-0.008480245722502167</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.689110186101023</v>
+        <v>2.912261853249491</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452227</v>
+        <v>4.122881758883809</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.689007868244185</v>
+        <v>2.917350000682992</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.145810686497816</v>
+        <v>-1.915057255987808</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.030327169331311</v>
+        <v>2.150970673974121</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.0621659400005582</v>
+        <v>-0.008480245722502167</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.65170830424385</v>
+        <v>2.912261853249491</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979534</v>
+        <v>4.122881758883809</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.694699430583131</v>
+        <v>2.917350000682992</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.412815196770251</v>
+        <v>-1.915057255987808</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9292169275612832</v>
+        <v>2.150970673974121</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2565289780435068</v>
+        <v>-0.008480245722502167</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.540782043757027</v>
+        <v>2.912261853249491</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230808</v>
+        <v>3.972913432880422</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.693903352479632</v>
+        <v>2.917350000682992</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.514012978207424</v>
+        <v>-1.915685550365793</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8879417368829157</v>
+        <v>2.150719356222928</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.324937791588826</v>
+        <v>-0.008480245722502167</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.498940677526337</v>
+        <v>2.912261853249491</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285455</v>
+        <v>3.976175639935069</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.691503314033949</v>
+        <v>2.914949962237309</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.481537392036651</v>
+        <v>-1.883209964195021</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8985319329055412</v>
+        <v>2.161309552245553</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.324937791588826</v>
+        <v>-0.008480245722502167</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.496540639080654</v>
+        <v>2.909861814803807</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848103</v>
+        <v>3.980114421497717</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.688028033242194</v>
+        <v>2.911474681445553</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.462499264329354</v>
+        <v>-1.864171836487723</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.902671903196705</v>
+        <v>2.165449522536717</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3831214029200205</v>
+        <v>-0.06666385705369671</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.458155191490182</v>
+        <v>2.871476367213336</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601253</v>
+        <v>4.001668451250868</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.865609902180875</v>
+        <v>3.089056550384234</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.493625895479973</v>
+        <v>-1.895298467638341</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.067803119675138</v>
+        <v>2.33058073901515</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3831214029200205</v>
+        <v>-0.06666385705369671</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.635737060428863</v>
+        <v>3.049058236152016</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537864</v>
+        <v>3.993051340187479</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.866443231167008</v>
+        <v>3.089889879370368</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.545946276080764</v>
+        <v>-1.947618848239133</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.047708296420955</v>
+        <v>2.310485915760967</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3481745429111484</v>
+        <v>-0.03171699704482456</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.657538505420319</v>
+        <v>3.070859681143473</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259121</v>
+        <v>4.14365685279531</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.872451761563934</v>
+        <v>3.095898409767293</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.690269182005683</v>
+        <v>-2.094150012231326</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9959876644479135</v>
+        <v>2.257881980561016</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3481745429111484</v>
+        <v>-0.03171699704482456</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.663547035817245</v>
+        <v>3.076868211540399</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989905</v>
+        <v>4.14365685279531</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.951604409355956</v>
+        <v>3.095898409767293</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.542526211770681</v>
+        <v>-2.094150012231326</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.134237500333936</v>
+        <v>2.257881980561016</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1803671856762652</v>
+        <v>-0.03171699704482456</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.843384097950197</v>
+        <v>3.076868211540399</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651167</v>
+        <v>4.14365685279531</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.954398030887437</v>
+        <v>3.095898409767293</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.644540894301902</v>
+        <v>-2.094150012231326</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.096225248852929</v>
+        <v>2.257881980561016</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1803671856762652</v>
+        <v>-0.03171699704482456</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.846177719481678</v>
+        <v>3.076868211540399</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864727</v>
+        <v>4.14365685279531</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.955060379279095</v>
+        <v>3.095898409767293</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.507931550207809</v>
+        <v>-2.094150012231326</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.151531334882224</v>
+        <v>2.257881980561016</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.04375784158217272</v>
+        <v>-0.03171699704482456</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.928805674329792</v>
+        <v>3.076868211540399</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360613</v>
+        <v>4.079055421818879</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.954140856019206</v>
+        <v>3.095898409767293</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.650696883030459</v>
+        <v>-2.100192050616473</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.093505678493274</v>
+        <v>2.255465165206957</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1865231744048231</v>
+        <v>-0.03171699704482456</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.842226951376312</v>
+        <v>3.076868211540399</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268424</v>
+        <v>4.148178263726688</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.020476409816026</v>
+        <v>3.162233963564114</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.588398884254337</v>
+        <v>-2.037894051840351</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.184760431800544</v>
+        <v>2.346719918514227</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1865231744048231</v>
+        <v>-0.03171699704482456</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.908562505173133</v>
+        <v>3.14320376533722</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462187</v>
+        <v>4.112180699617269</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.729057282205424</v>
+        <v>2.870814835953512</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.386608686589179</v>
+        <v>-2.027764882831608</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9740573832560055</v>
+        <v>2.059352458507122</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.01149501776433126</v>
+        <v>-0.02296783088528065</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.735954292864023</v>
+        <v>2.857034137422344</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841441242322421</v>
+        <v>4.122777641260166</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.7993475145276</v>
+        <v>2.870814835953512</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.326718004946586</v>
+        <v>-2.03088929876369</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.068303888235218</v>
+        <v>2.058102692134289</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.07138569940692474</v>
+        <v>-0.02296783088528065</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.842178934171755</v>
+        <v>2.857034137422344</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819059724789543</v>
+        <v>4.130842596346223</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.813975250643643</v>
+        <v>2.885442572069556</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.42445854957156</v>
+        <v>-2.127708257127904</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.043835406501272</v>
+        <v>2.034002844904647</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.05549642127394455</v>
+        <v>-0.04049972060132079</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.84727310340801</v>
+        <v>2.861142739708764</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,45 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831815456959383</v>
+        <v>4.112440231527782</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.812511231468315</v>
+        <v>2.885442572069556</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.430610188429458</v>
+        <v>-2.128013845828054</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.039910731782784</v>
+        <v>2.034002844904647</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.04934478241604651</v>
+        <v>-0.04049972060132079</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.842118100917943</v>
-      </c>
-    </row>
-    <row r="1975">
-      <c r="A1975" s="2" t="n">
-        <v>45437</v>
-      </c>
-      <c r="B1975" t="n">
-        <v>3.89456553753201</v>
-      </c>
-      <c r="C1975" t="n">
-        <v>2.946529248364446</v>
-      </c>
-      <c r="D1975" t="n">
-        <v>-4.430610188429458</v>
-      </c>
-      <c r="E1975" t="n">
-        <v>1.039910731782784</v>
-      </c>
-      <c r="F1975" t="n">
-        <v>0.04934478241604651</v>
-      </c>
-      <c r="G1975" t="n">
-        <v>2.939593045350814</v>
+        <v>2.861142739708764</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240525.xlsx
+++ b/tame_output/ON/bt/strategyON_20240525.xlsx
@@ -605,17 +605,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>394</v>
+        <v>342</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>83.2%</t>
+          <t>55.0%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,35 +791,35 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-30.1%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-51.0%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>127.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-518.1%</t>
+          <t>-665.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,47 +992,47 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>439.8%</t>
+          <t>449.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-374.4%</t>
+          <t>-623.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-205.1%</t>
+          <t>-266.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,47 +1150,47 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-172.8%</t>
+          <t>-279.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,27 +1293,27 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-248.1%</t>
+          <t>-292.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-187.1%</t>
+          <t>-137.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-228.0%</t>
+          <t>-246.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-146.7%</t>
+          <t>-175.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-28.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-159.9%</t>
+          <t>-177.7%</t>
         </is>
       </c>
     </row>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386097</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998564</v>
+        <v>3.367370539998565</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082129</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757927</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153011</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382195</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.925690004306867</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.565157061035161</v>
+        <v>-3.565657023012474</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.711671289024434</v>
+        <v>1.711471304233509</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.2413167039278764</v>
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.925690004306867</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
-        <v>3.138090537752246</v>
+        <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.565157061035161</v>
+        <v>-3.909339796239137</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.711671289024434</v>
+        <v>1.57576731839746</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-0.3492227559550946</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.993300515395521</v>
+        <v>2.930326007633806</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.925690004306867</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
-        <v>3.138090537752246</v>
+        <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.565157061035161</v>
+        <v>-4.115851573126158</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.711671289024434</v>
+        <v>1.489268666298909</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-0.555734532842116</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.993300515395521</v>
+        <v>2.802525000157851</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.925690004306867</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
-        <v>3.138090537752246</v>
+        <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.565157061035161</v>
+        <v>-4.371692658904851</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.711671289024434</v>
+        <v>1.388705158687692</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-0.555734532842116</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.993300515395521</v>
+        <v>2.80429792685811</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.925690004306867</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
-        <v>3.138090537752246</v>
+        <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.565157061035161</v>
+        <v>-4.803498452054638</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.711671289024434</v>
+        <v>1.202315728895181</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-0.692152029283383</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.993300515395521</v>
+        <v>2.708780316460754</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.925690004306867</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
-        <v>3.138090537752246</v>
+        <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.565157061035161</v>
+        <v>-5.038192446187191</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.711671289024434</v>
+        <v>1.096722906244251</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-0.6858157620541279</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.993300515395521</v>
+        <v>2.700866851800398</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.925690004306867</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
-        <v>3.138090537752246</v>
+        <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.565157061035161</v>
+        <v>-5.373855093417643</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.711671289024434</v>
+        <v>0.9610384390080351</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-0.6858157620541279</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.993300515395521</v>
+        <v>2.699447443456363</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.925690004306867</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
-        <v>3.138090537752246</v>
+        <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-3.565157061035161</v>
+        <v>-5.737481338317957</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.711671289024434</v>
+        <v>0.8220755012821512</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-0.7840373989212537</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.993300515395521</v>
+        <v>2.647002021570329</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.925690004306867</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
-        <v>3.138090537752246</v>
+        <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-3.565157061035161</v>
+        <v>-6.102608720956703</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.711671289024434</v>
+        <v>0.6752790632324839</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-1.080348183220266</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.993300515395521</v>
+        <v>2.468470065996753</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.925690004306867</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.138090537752246</v>
+        <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-3.565157061035161</v>
+        <v>-6.511197498137381</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.711671289024434</v>
+        <v>0.510605096374972</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.993300515395521</v>
+        <v>2.222078343703105</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.925690004306867</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.138090537752246</v>
+        <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-3.565157061035161</v>
+        <v>-6.787773598453214</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.711671289024434</v>
+        <v>0.3951600887200994</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.993300515395521</v>
+        <v>2.217263776174566</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.925690004306867</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.138090537752246</v>
+        <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-3.565157061035161</v>
+        <v>-7.204165472740211</v>
       </c>
       <c r="E1866" t="n">
-        <v>1.711671289024434</v>
+        <v>0.2265973896141777</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.993300515395521</v>
+        <v>2.215257826783443</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.925690004306867</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.138090537752246</v>
+        <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-3.565157061035161</v>
+        <v>-7.520777415280859</v>
       </c>
       <c r="E1867" t="n">
-        <v>1.711671289024434</v>
+        <v>0.1102113032665977</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.993300515395521</v>
+        <v>2.225516517452122</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.925690004306867</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.138090537752246</v>
+        <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-3.565157061035161</v>
+        <v>-7.866652237265669</v>
       </c>
       <c r="E1868" t="n">
-        <v>1.711671289024434</v>
+        <v>-0.03203906038163096</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.993300515395521</v>
+        <v>2.221616082597818</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.925690004306867</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.138090537752246</v>
+        <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-3.565157061035161</v>
+        <v>-8.030232115450053</v>
       </c>
       <c r="E1869" t="n">
-        <v>1.711671289024434</v>
+        <v>-0.09906609160038382</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.993300515395521</v>
+        <v>2.220021002652818</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.925690004306867</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.138090537752246</v>
+        <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-3.565157061035161</v>
+        <v>-8.326893457260251</v>
       </c>
       <c r="E1870" t="n">
-        <v>1.711671289024434</v>
+        <v>-0.2139516523952549</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.993300515395521</v>
+        <v>2.182554097141699</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.925690004306867</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.138090537752246</v>
+        <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-3.565157061035161</v>
+        <v>-8.531924638034567</v>
       </c>
       <c r="E1871" t="n">
-        <v>1.711671289024434</v>
+        <v>-0.2999904292393847</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.993300515395521</v>
+        <v>2.178527792607296</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.925690004306867</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.138090537752246</v>
+        <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-3.565157061035161</v>
+        <v>-8.914926026777199</v>
       </c>
       <c r="E1872" t="n">
-        <v>1.711671289024434</v>
+        <v>-0.4532930860580211</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.993300515395521</v>
+        <v>2.178425691285712</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.925690004306867</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.138090537752246</v>
+        <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-3.565157061035161</v>
+        <v>-9.096795817762233</v>
       </c>
       <c r="E1873" t="n">
-        <v>1.711671289024434</v>
+        <v>-0.5234694864806047</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-1.739549887119858</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.993300515395521</v>
+        <v>2.071875332666121</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.925690004306867</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.138090537752246</v>
+        <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-3.565157061035161</v>
+        <v>-9.456326140266235</v>
       </c>
       <c r="E1874" t="n">
-        <v>1.711671289024434</v>
+        <v>-0.661931312184155</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-1.739549887119858</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.993300515395521</v>
+        <v>2.077225635964171</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.925690004306867</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.138090537752246</v>
+        <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-3.565157061035161</v>
+        <v>-9.506675203720457</v>
       </c>
       <c r="E1875" t="n">
-        <v>1.711671289024434</v>
+        <v>-0.6741549176086665</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-1.78989895057408</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.993300515395521</v>
+        <v>2.054932217848815</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.925690004306867</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.138090537752246</v>
+        <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-3.565157061035161</v>
+        <v>-9.604294481141853</v>
       </c>
       <c r="E1876" t="n">
-        <v>1.711671289024434</v>
+        <v>-0.710160877955456</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-1.887518227995477</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.993300515395521</v>
+        <v>1.999402402017747</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.685768606310301</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.138090537752246</v>
+        <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-3.561466136078749</v>
+        <v>-9.751820569147496</v>
       </c>
       <c r="E1877" t="n">
-        <v>1.713147659006999</v>
+        <v>-0.766277756836141</v>
       </c>
       <c r="F1877" t="n">
-        <v>-0.2413167039278764</v>
+        <v>-2.03504431600112</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.993300515395521</v>
+        <v>1.913780305535933</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.696110293514505</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.143603734870888</v>
+        <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-3.765724311408613</v>
+        <v>-9.95607874447736</v>
       </c>
       <c r="E1878" t="n">
-        <v>1.636957585993696</v>
+        <v>-0.8424678298494443</v>
       </c>
       <c r="F1878" t="n">
-        <v>-0.3689556485418652</v>
+        <v>-2.162683260615109</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.922230345745769</v>
+        <v>1.842710135886182</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.690171799102695</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.148086289355324</v>
+        <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-3.9075340856154</v>
+        <v>-10.09788851868415</v>
       </c>
       <c r="E1879" t="n">
-        <v>1.584716230795417</v>
+        <v>-0.8947091850477231</v>
       </c>
       <c r="F1879" t="n">
-        <v>-0.5402344461874405</v>
+        <v>-2.333962058260685</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.82394562164286</v>
+        <v>1.744425411783272</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.693291633813439</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.163457990848745</v>
+        <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-3.834064253947952</v>
+        <v>-10.0244186870167</v>
       </c>
       <c r="E1880" t="n">
-        <v>1.629475864955817</v>
+        <v>-0.8499495508873229</v>
       </c>
       <c r="F1880" t="n">
-        <v>-0.4667646145199921</v>
+        <v>-2.260492226593236</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.883399222136751</v>
+        <v>1.803879012277163</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.683379135981407</v>
+        <v>3.490059241608603</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.178013211596262</v>
+        <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-4.009188671334496</v>
+        <v>-10.19954310440324</v>
       </c>
       <c r="E1881" t="n">
-        <v>1.573981318748717</v>
+        <v>-0.9054440970944233</v>
       </c>
       <c r="F1881" t="n">
-        <v>-0.641889031906536</v>
+        <v>-2.43561664397978</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.792879792452341</v>
+        <v>1.713359582592753</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.67919848878308</v>
+        <v>3.485878594410276</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.170794046694666</v>
+        <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-4.243640765348986</v>
+        <v>-10.43399519841773</v>
       </c>
       <c r="E1882" t="n">
-        <v>1.472981316241325</v>
+        <v>-1.006444099601815</v>
       </c>
       <c r="F1882" t="n">
-        <v>-0.641889031906536</v>
+        <v>-2.43561664397978</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.785660627550745</v>
+        <v>1.706140417691157</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.674012387137205</v>
+        <v>3.480692492764401</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.16412185592069</v>
+        <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-4.531444609886224</v>
+        <v>-10.72179904295497</v>
       </c>
       <c r="E1883" t="n">
-        <v>1.351187587652453</v>
+        <v>-1.128237828190687</v>
       </c>
       <c r="F1883" t="n">
-        <v>-0.9296928764437741</v>
+        <v>-2.723420488517018</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.606306130054426</v>
+        <v>1.526785920194838</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.687035908763395</v>
+        <v>3.49371601439059</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.165237645759246</v>
+        <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-4.58423076548655</v>
+        <v>-10.7745851985553</v>
       </c>
       <c r="E1884" t="n">
-        <v>1.331188915250879</v>
+        <v>-1.148236500592261</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.025368363026171</v>
+        <v>-2.819095975099415</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.550016627943544</v>
+        <v>1.470496418083956</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.685421535670209</v>
+        <v>3.492101641297404</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.167931374388361</v>
+        <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-4.816259685222811</v>
+        <v>-11.00661411829156</v>
       </c>
       <c r="E1885" t="n">
-        <v>1.241071075985489</v>
+        <v>-1.238354339857651</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.087381060214594</v>
+        <v>-2.881108672287839</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.515502738259605</v>
+        <v>1.435982528400017</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.766993919695353</v>
+        <v>3.573674025322548</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.171921710074762</v>
+        <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-4.764244171253999</v>
+        <v>-10.95459860432275</v>
       </c>
       <c r="E1886" t="n">
-        <v>1.265867617259415</v>
+        <v>-1.213557798583725</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.087381060214594</v>
+        <v>-2.881108672287839</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.519493073946006</v>
+        <v>1.439972864086418</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.793358159531731</v>
+        <v>3.600038265158926</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.17044648317602</v>
+        <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-4.90591601297812</v>
+        <v>-11.09627044604687</v>
       </c>
       <c r="E1887" t="n">
-        <v>1.207723653671025</v>
+        <v>-1.271701762172115</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.087381060214594</v>
+        <v>-2.881108672287839</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.518017847047264</v>
+        <v>1.438497637187676</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.884891628313525</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.185499893340892</v>
+        <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-4.856325168553286</v>
+        <v>-11.04667960162203</v>
       </c>
       <c r="E1888" t="n">
-        <v>1.242613401605831</v>
+        <v>-1.236812014237309</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.03779021578976</v>
+        <v>-2.831517827863005</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.562825763867036</v>
+        <v>1.483305554007449</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.870161444143385</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.172448759694209</v>
+        <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-4.657173061316187</v>
+        <v>-10.84752749438493</v>
       </c>
       <c r="E1889" t="n">
-        <v>1.309223110853987</v>
+        <v>-1.170202304989152</v>
       </c>
       <c r="F1889" t="n">
-        <v>-0.8724676898399472</v>
+        <v>-2.666195301913191</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.648968145790241</v>
+        <v>1.569447935930654</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.878481275988087</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.182027832730418</v>
+        <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-4.431327908596776</v>
+        <v>-10.62168234166552</v>
       </c>
       <c r="E1890" t="n">
-        <v>1.40914024497796</v>
+        <v>-1.070285170865179</v>
       </c>
       <c r="F1890" t="n">
-        <v>-0.8305410142527835</v>
+        <v>-2.624268626326028</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.683703224178748</v>
+        <v>1.60418301431916</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.832339160005338</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.183166977286477</v>
+        <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-4.316111455041868</v>
+        <v>-10.49710368532793</v>
       </c>
       <c r="E1891" t="n">
-        <v>1.456365970955983</v>
+        <v>-1.019314563774083</v>
       </c>
       <c r="F1891" t="n">
-        <v>-0.8305410142527835</v>
+        <v>-2.624268626326028</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.684842368734807</v>
+        <v>1.605322158875219</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.832339160005338</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.183166977286477</v>
+        <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-4.316111455041868</v>
+        <v>-10.54999897337222</v>
       </c>
       <c r="E1892" t="n">
-        <v>1.456365970955983</v>
+        <v>-1.037838904829691</v>
       </c>
       <c r="F1892" t="n">
-        <v>-0.8305410142527835</v>
+        <v>-2.619313280237582</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.684842368734807</v>
+        <v>1.610929140690395</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.832339160005338</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.183166977286477</v>
+        <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-4.316111455041868</v>
+        <v>-10.26609024244347</v>
       </c>
       <c r="E1893" t="n">
-        <v>1.456365970955983</v>
+        <v>-0.9185417082195544</v>
       </c>
       <c r="F1893" t="n">
-        <v>-0.8305410142527835</v>
+        <v>-2.619313280237582</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.684842368734807</v>
+        <v>1.616662844929031</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.832339160005338</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.183166977286477</v>
+        <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-4.316111455041868</v>
+        <v>-10.19472384983382</v>
       </c>
       <c r="E1894" t="n">
-        <v>1.456365970955983</v>
+        <v>-0.899732413569561</v>
       </c>
       <c r="F1894" t="n">
-        <v>-0.8305410142527835</v>
+        <v>-2.547946887627934</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.684842368734807</v>
+        <v>1.649745418100955</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.832339160005338</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.183166977286477</v>
+        <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-4.316111455041868</v>
+        <v>-9.930886982629751</v>
       </c>
       <c r="E1895" t="n">
-        <v>1.456365970955983</v>
+        <v>-0.8040811480008405</v>
       </c>
       <c r="F1895" t="n">
-        <v>-0.8305410142527835</v>
+        <v>-2.547946887627934</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.684842368734807</v>
+        <v>1.639861936788047</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.832339160005338</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.183166977286477</v>
+        <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-4.316111455041868</v>
+        <v>-9.663645181761353</v>
       </c>
       <c r="E1896" t="n">
-        <v>1.456365970955983</v>
+        <v>-0.6990189881528552</v>
       </c>
       <c r="F1896" t="n">
-        <v>-0.8305410142527835</v>
+        <v>-2.547946887627934</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.684842368734807</v>
+        <v>1.638027376288673</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.832339160005338</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.183166977286477</v>
+        <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-4.316111455041868</v>
+        <v>-9.565738143084863</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.456365970955983</v>
+        <v>-0.66015648765572</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.8305410142527835</v>
+        <v>-2.479961137767377</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.684842368734807</v>
+        <v>1.678518511231546</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.832339160005338</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.183166977286477</v>
+        <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-4.316111455041868</v>
+        <v>-9.541784602108905</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.456365970955983</v>
+        <v>-0.649906565119843</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.8305410142527835</v>
+        <v>-2.45600759679142</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.684842368734807</v>
+        <v>1.693559141962615</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.832339160005338</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.183166977286477</v>
+        <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-4.316111455041868</v>
+        <v>-9.277724663786108</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.456365970955983</v>
+        <v>-0.5575429059524764</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.8305410142527835</v>
+        <v>-2.191947658468624</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.684842368734807</v>
+        <v>1.83873478879454</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.832339160005338</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.183166977286477</v>
+        <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.316111455041868</v>
+        <v>-8.570645040281271</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.456365970955983</v>
+        <v>-0.2774980902108424</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.8305410142527835</v>
+        <v>-2.191947658468624</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.684842368734807</v>
+        <v>1.835947755134239</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.832339160005338</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.183166977286477</v>
+        <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.316111455041868</v>
+        <v>-8.53046074191508</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.456365970955983</v>
+        <v>-0.2610807469765248</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.8305410142527835</v>
+        <v>-2.151763360102433</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.684842368734807</v>
+        <v>1.860401958041795</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.832339160005338</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.183166977286477</v>
+        <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.316111455041868</v>
+        <v>-8.450390946377276</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.456365970955983</v>
+        <v>-0.2296860075406464</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8305410142527835</v>
+        <v>-2.071693564564629</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.684842368734807</v>
+        <v>1.907810656585234</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.985288251388841</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.183166977286477</v>
+        <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.304845061268599</v>
+        <v>-8.216909724147676</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.46087252846529</v>
+        <v>-0.128369089810954</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8305410142527835</v>
+        <v>-1.838212342335031</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.684842368734807</v>
+        <v>2.055823818760846</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.999594944882818</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.180274766973518</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.155178670261084</v>
+        <v>-8.067243333140162</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.517846874555337</v>
+        <v>-0.07139474372090771</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7376375230102475</v>
+        <v>-1.745308851092495</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.73769225316737</v>
+        <v>2.108673703193408</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.961140070487461</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.175642253720545</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.022903196630198</v>
+        <v>-7.934967859509276</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.566124550754719</v>
+        <v>-0.02311706752152576</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6053620493793609</v>
+        <v>-1.613033377461608</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.812425024092929</v>
+        <v>2.183406474118967</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.982676616202987</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.178457314408182</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.832303521957045</v>
+        <v>-7.744368184836123</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.645179481311616</v>
+        <v>0.05593786303537174</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.414762374706208</v>
+        <v>-1.422433702788455</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.929599889584457</v>
+        <v>2.300581339610495</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.951840394058022</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.19136365563184</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.583303723273465</v>
+        <v>-7.495368386152542</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.757685742008707</v>
+        <v>0.168444123732463</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.414762374706208</v>
+        <v>-1.422433702788455</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.942506230808116</v>
+        <v>2.313487680834154</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.890889677704678</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.063387726032621</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.688893713046569</v>
+        <v>-7.600958375925646</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.587473816500246</v>
+        <v>-0.001767801775997668</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.5203523644793124</v>
+        <v>-1.528023692561559</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.751176307345034</v>
+        <v>2.122157757371073</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.968380406084933</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.111932067909708</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.707628615165166</v>
+        <v>-7.619693278044243</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.628524197529894</v>
+        <v>0.03928257925364997</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.5203523644793124</v>
+        <v>-1.528023692561559</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.79972064922212</v>
+        <v>2.170702099248159</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.958291508807842</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.99205314522154</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.559688573757567</v>
+        <v>-7.471753236636644</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.567821291404766</v>
+        <v>-0.02142032687147788</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5000314485707549</v>
+        <v>-1.507702776653002</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.692034276079087</v>
+        <v>2.063015726105126</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.921524051506236</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.983339158968062</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.542530423626272</v>
+        <v>-7.45459508650535</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.565970565203806</v>
+        <v>-0.02327105307243826</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.4828732984394606</v>
+        <v>-1.490544626521707</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.693615179904386</v>
+        <v>2.064596629930425</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.927927538195142</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.976378546872969</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-3.498982016855582</v>
+        <v>-7.411046679734659</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.576429315816989</v>
+        <v>-0.01281230245925524</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.4828732984394606</v>
+        <v>-1.490544626521707</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.686654567809293</v>
+        <v>2.057636017835332</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.980880355590454</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.990840901254112</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-3.256833623401724</v>
+        <v>-7.168898286280801</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.687751027579675</v>
+        <v>0.09850940930343111</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.4828732984394606</v>
+        <v>-1.490544626521707</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.701116922190436</v>
+        <v>2.072098372216475</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>4.026509308819852</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.985373021713307</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-3.193604251633376</v>
+        <v>-7.105668914512453</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.707574896746209</v>
+        <v>0.1183332784699656</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.4828732984394606</v>
+        <v>-1.490544626521707</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.695649042649631</v>
+        <v>2.06663049267567</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>4.026010750889082</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.982871115723884</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-3.070313116816245</v>
+        <v>-6.982377779695322</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.754389444683638</v>
+        <v>0.1651478264073947</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.3595821636223301</v>
+        <v>-1.367253491704577</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.767121817550486</v>
+        <v>2.138103267576525</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>4.010411501016945</v>
+        <v>3.812453678919912</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.990572093961209</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-3.049163917912802</v>
+        <v>-6.961228580791879</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.770550102482341</v>
+        <v>0.181308484206097</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3384329647188868</v>
+        <v>-1.346104292801134</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.787512315129877</v>
+        <v>2.158493765155916</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.946286230415129</v>
+        <v>3.748328408318097</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.98635280230826</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-2.805398475929358</v>
+        <v>-6.717463138808434</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.863836987622769</v>
+        <v>0.2745953693465255</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3384329647188868</v>
+        <v>-1.346104292801134</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.783293023476928</v>
+        <v>2.154274473502967</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>4.02226905515456</v>
+        <v>3.824311233057528</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.988477116228275</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-2.658501448211487</v>
+        <v>-6.570566111090564</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.924720112629934</v>
+        <v>0.3354784943536897</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.2907747227402988</v>
+        <v>-1.298446050822545</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.814012282584097</v>
+        <v>2.184993732610136</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>4.024312796376217</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.981219191211978</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-2.408651054262413</v>
+        <v>-6.320715717141489</v>
       </c>
       <c r="E1919" t="n">
-        <v>2.017402345193265</v>
+        <v>0.4281607269170218</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.2907747227402988</v>
+        <v>-1.298446050822545</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.806754357567799</v>
+        <v>2.177735807593838</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>4.033915809108529</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.984818314732626</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-2.23275896179498</v>
+        <v>-6.144823624674057</v>
       </c>
       <c r="E1920" t="n">
-        <v>2.091358305700887</v>
+        <v>0.5021166874246434</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.2907747227402988</v>
+        <v>-1.298446050822545</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.810353481088447</v>
+        <v>2.181334931114487</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.860755523105283</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.99814582078718</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-2.073664045121362</v>
+        <v>-5.973377161651594</v>
       </c>
       <c r="E1921" t="n">
-        <v>2.168323778424888</v>
+        <v>0.5840227786881824</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.1316798060666801</v>
+        <v>-1.126999587800082</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.919137937147172</v>
+        <v>2.297530314982518</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.860755523105283</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.99814582078718</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-2.073664045121362</v>
+        <v>-5.748344161982771</v>
       </c>
       <c r="E1922" t="n">
-        <v>2.168323778424888</v>
+        <v>0.6730564561720089</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1316798060666801</v>
+        <v>-0.9019665881312596</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.919137937147172</v>
+        <v>2.431570592400109</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.860755523105283</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.99814582078718</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-2.073664045121362</v>
+        <v>-5.684708419748836</v>
       </c>
       <c r="E1923" t="n">
-        <v>2.168323778424888</v>
+        <v>0.7032055541198998</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.1316798060666801</v>
+        <v>-0.8383308458973251</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.919137937147172</v>
+        <v>2.474446838794787</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.860755523105283</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.99814582078718</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-2.073664045121362</v>
+        <v>-5.591708378542938</v>
       </c>
       <c r="E1924" t="n">
-        <v>2.168323778424888</v>
+        <v>0.7215998293860548</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.1316798060666801</v>
+        <v>-0.8383308458973251</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.919137937147172</v>
+        <v>2.455641097578583</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.860755523105283</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.99814582078718</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-2.073664045121362</v>
+        <v>-5.351277881738078</v>
       </c>
       <c r="E1925" t="n">
-        <v>2.168323778424888</v>
+        <v>0.8195151047328761</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.1316798060666801</v>
+        <v>-0.5979003490924648</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.919137937147172</v>
+        <v>2.601642472286376</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.860755523105283</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.99814582078718</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-2.073664045121362</v>
+        <v>-5.279035313566883</v>
       </c>
       <c r="E1926" t="n">
-        <v>2.168323778424888</v>
+        <v>0.8523414458361742</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.1316798060666801</v>
+        <v>-0.5979003490924648</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.919137937147172</v>
+        <v>2.605571786121196</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.860755523105283</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.99814582078718</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-2.073664045121362</v>
+        <v>-5.226036991285495</v>
       </c>
       <c r="E1927" t="n">
-        <v>2.168323778424888</v>
+        <v>0.8742193586660694</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.1316798060666801</v>
+        <v>-0.542564090090526</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.919137937147172</v>
+        <v>2.639452125439699</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.860755523105283</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.99814582078718</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-2.073664045121362</v>
+        <v>-5.117232105805768</v>
       </c>
       <c r="E1928" t="n">
-        <v>2.168323778424888</v>
+        <v>0.9147393840779539</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.1316798060666801</v>
+        <v>-0.542564090090526</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.919137937147172</v>
+        <v>2.636450196659693</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.860755523105283</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.99814582078718</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-2.073664045121362</v>
+        <v>-4.897211307768758</v>
       </c>
       <c r="E1929" t="n">
-        <v>2.168323778424888</v>
+        <v>1.004326740303372</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.1316798060666801</v>
+        <v>-0.4013442450225457</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.919137937147172</v>
+        <v>2.722761140711095</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.860755523105283</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.99814582078718</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-2.073664045121362</v>
+        <v>-4.76434361870548</v>
       </c>
       <c r="E1930" t="n">
-        <v>2.168323778424888</v>
+        <v>1.073367998730506</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.1316798060666801</v>
+        <v>-0.4013442450225457</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.919137937147172</v>
+        <v>2.738655323512919</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>4.076849183395007</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.99814582078718</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-2.079691069651433</v>
+        <v>-4.60482851518611</v>
       </c>
       <c r="E1931" t="n">
-        <v>2.165912968612859</v>
+        <v>1.138319884578556</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1316798060666801</v>
+        <v>-0.2418291415031758</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.919137937147172</v>
+        <v>2.835510230064842</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>4.023075348475745</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.00823392334862</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-1.935018924551696</v>
+        <v>-4.460156370086373</v>
       </c>
       <c r="E1932" t="n">
-        <v>2.233869929214194</v>
+        <v>1.206276845179891</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.0129923390330573</v>
+        <v>-0.09715699640343839</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.016029326768455</v>
+        <v>2.932401619686125</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.967641019840853</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.994271414750046</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-1.994893751909388</v>
+        <v>-4.520031197444065</v>
       </c>
       <c r="E1933" t="n">
-        <v>2.195957489672543</v>
+        <v>1.16836440563824</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.04688248832463482</v>
+        <v>-0.1570318237611305</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.966141921755265</v>
+        <v>2.882514214672935</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.994449274573265</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.016671908072612</v>
+        <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-1.908094254130379</v>
+        <v>-4.433231699665056</v>
       </c>
       <c r="E1934" t="n">
-        <v>2.253077782106713</v>
+        <v>1.22548469807241</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.04688248832463482</v>
+        <v>-0.1570318237611305</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.988542415077831</v>
+        <v>2.904914707995502</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.960948195329442</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.016744309446024</v>
+        <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-1.910563960592186</v>
+        <v>-4.435701406126862</v>
       </c>
       <c r="E1935" t="n">
-        <v>2.252162300895403</v>
+        <v>1.2245692168611</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.04935219478644098</v>
+        <v>-0.1595015302229367</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.98713299257416</v>
+        <v>2.90350528549183</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.975021992902346</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.027751231920726</v>
+        <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-1.978934146916195</v>
+        <v>-4.504071592450872</v>
       </c>
       <c r="E1936" t="n">
-        <v>2.2358211488405</v>
+        <v>1.208228064806197</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.04007649575022604</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.003705334470591</v>
+        <v>2.920077627388261</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>4.065275545303483</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.018187940552617</v>
+        <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-2.087211390244628</v>
+        <v>-4.612609773367006</v>
       </c>
       <c r="E1937" t="n">
-        <v>2.182946960141019</v>
+        <v>1.155249501071635</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.04007649575022604</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.994142043102482</v>
+        <v>2.910514336020152</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>4.065275545303483</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
-        <v>3.018187940552617</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-2.087211390244628</v>
+        <v>-4.643602932695711</v>
       </c>
       <c r="E1938" t="n">
-        <v>2.182946960141019</v>
+        <v>0.9675618023805399</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.04007649575022604</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.994142043102482</v>
+        <v>2.735223901060539</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>4.065275545303483</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
-        <v>3.018187940552617</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-2.087211390244628</v>
+        <v>-4.468128672903243</v>
       </c>
       <c r="E1939" t="n">
-        <v>2.182946960141019</v>
+        <v>1.042318738289315</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.04007649575022604</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.994142043102482</v>
+        <v>2.739791133052327</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>4.065275545303483</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>3.018187940552617</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-2.087211390244628</v>
+        <v>-4.579064925544492</v>
       </c>
       <c r="E1940" t="n">
-        <v>2.182946960141019</v>
+        <v>0.9736862659940226</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.04007649575022604</v>
+        <v>-0.1502258311867217</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.994142043102482</v>
+        <v>2.715533161813534</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>4.009236955567262</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
-        <v>3.018187940552617</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-2.085558974765537</v>
+        <v>-4.782091503087725</v>
       </c>
       <c r="E1941" t="n">
-        <v>2.183607926332655</v>
+        <v>0.8956070201966349</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.04007649575022604</v>
+        <v>-0.3532524087299551</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.994142043102482</v>
+        <v>2.596848600507499</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>4.020370610720131</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
-        <v>3.02836032698475</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-1.927633375830245</v>
+        <v>-4.624165904152432</v>
       </c>
       <c r="E1942" t="n">
-        <v>2.256950552338905</v>
+        <v>0.9689496462028844</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.04007649575022604</v>
+        <v>-0.3532524087299551</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.004314429534614</v>
+        <v>2.607020986939632</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>4.022976616198267</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
-        <v>3.02330659755861</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-1.841389912803867</v>
+        <v>-4.537922441126054</v>
       </c>
       <c r="E1943" t="n">
-        <v>2.286394208123316</v>
+        <v>0.9983933019872959</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.04007649575022604</v>
+        <v>-0.3532524087299551</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.999260700108475</v>
+        <v>2.601967257513492</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.988054157772015</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>3.015082373003136</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-1.842572997454928</v>
+        <v>-4.539105525777115</v>
       </c>
       <c r="E1944" t="n">
-        <v>2.277696749707417</v>
+        <v>0.9896958435713969</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.04571954421673757</v>
+        <v>-0.3588954571964666</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.987650646473093</v>
+        <v>2.59035720387811</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.989597824259162</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>3.015634246036237</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-1.879794956940722</v>
+        <v>-4.415977818783032</v>
       </c>
       <c r="E1945" t="n">
-        <v>2.263359838946201</v>
+        <v>1.039498799402132</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.04571954421673757</v>
+        <v>-0.3588954571964666</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.988202519506195</v>
+        <v>2.590909076911212</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.969417259265471</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.944906937927603</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-1.786984475489863</v>
+        <v>-4.323167337332173</v>
       </c>
       <c r="E1946" t="n">
-        <v>2.229756723417911</v>
+        <v>1.005895683873841</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.04709093723412178</v>
+        <v>-0.2660849757456073</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.973161500268076</v>
+        <v>2.575868057673093</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.984312475016399</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.946780413852204</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-1.738421423268833</v>
+        <v>-4.274604285111143</v>
       </c>
       <c r="E1947" t="n">
-        <v>2.251055420230923</v>
+        <v>1.027194380686854</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.09565398945515197</v>
+        <v>-0.2175219235245771</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.004172807525295</v>
+        <v>2.606879364930312</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.957103853928711</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.941856122363927</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-1.625750205032582</v>
+        <v>-4.161933066874893</v>
       </c>
       <c r="E1948" t="n">
-        <v>2.291199616037146</v>
+        <v>1.067338576493077</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.2083252076914022</v>
+        <v>-0.1048507052883269</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.066851246978768</v>
+        <v>2.669557804383786</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.979074262254509</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.947347418194594</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-1.51337320384991</v>
+        <v>-4.04955606569222</v>
       </c>
       <c r="E1949" t="n">
-        <v>2.341641712340883</v>
+        <v>1.117780672796813</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.2083252076914022</v>
+        <v>-0.1048507052883269</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.072342542809436</v>
+        <v>2.675049100214453</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.925624498954833</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.958844619963133</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-1.71160777273664</v>
+        <v>-4.24779063457895</v>
       </c>
       <c r="E1950" t="n">
-        <v>2.273845086554729</v>
+        <v>1.04998404701066</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.01009063880467159</v>
+        <v>-0.3030852741750575</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.964899003245936</v>
+        <v>2.567605560650954</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.879096280161293</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.797200339963786</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-1.794609053761919</v>
+        <v>-4.330791915604229</v>
       </c>
       <c r="E1951" t="n">
-        <v>2.079000294145271</v>
+        <v>0.8551392546012018</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.008480245722502167</v>
+        <v>-0.3216561587022312</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.792112192530285</v>
+        <v>2.394818749935302</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>4.122881758883809</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.917350000682992</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-1.915057255987808</v>
+        <v>-4.457858921911217</v>
       </c>
       <c r="E1952" t="n">
-        <v>2.150970673974121</v>
+        <v>0.9244621127976123</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.008480245722502167</v>
+        <v>-0.3216561587022312</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.912261853249491</v>
+        <v>2.514968410654508</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>4.122881758883809</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.917350000682992</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-1.915057255987808</v>
+        <v>-4.54445750489232</v>
       </c>
       <c r="E1953" t="n">
-        <v>2.150970673974121</v>
+        <v>0.9043357057074941</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.008480245722502167</v>
+        <v>-0.3216561587022312</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.912261853249491</v>
+        <v>2.529481436756831</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>4.122881758883809</v>
+        <v>3.741174069913421</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.917350000682992</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-1.915057255987808</v>
+        <v>-4.506073842334169</v>
       </c>
       <c r="E1954" t="n">
-        <v>2.150970673974121</v>
+        <v>0.9171086120731231</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.008480245722502167</v>
+        <v>-0.2832724961440801</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.912261853249491</v>
+        <v>2.54993107563409</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>4.122881758883809</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.917350000682992</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-1.915057255987808</v>
+        <v>-4.328957512299003</v>
       </c>
       <c r="E1955" t="n">
-        <v>2.150970673974121</v>
+        <v>0.9846841729324916</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.008480245722502167</v>
+        <v>-0.2832724961440801</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.912261853249491</v>
+        <v>2.546660104479392</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>4.122881758883809</v>
+        <v>3.741328448793898</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.917350000682992</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-1.915057255987808</v>
+        <v>-4.29925538832271</v>
       </c>
       <c r="E1956" t="n">
-        <v>2.150970673974121</v>
+        <v>0.9972484142849221</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.008480245722502167</v>
+        <v>-0.2877426213593934</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.912261853249491</v>
+        <v>2.544661421112117</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>4.122881758883809</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.917350000682992</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-1.915057255987808</v>
+        <v>-4.119879967083942</v>
       </c>
       <c r="E1957" t="n">
-        <v>2.150970673974121</v>
+        <v>1.062785558086843</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.008480245722502167</v>
+        <v>-0.1309658631886748</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.912261853249491</v>
+        <v>2.632514451320963</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>4.122881758883809</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.917350000682992</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-1.915057255987808</v>
+        <v>-4.164894180604549</v>
       </c>
       <c r="E1958" t="n">
-        <v>2.150970673974121</v>
+        <v>1.025587328010191</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.008480245722502167</v>
+        <v>-0.1613147585032794</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.912261853249491</v>
+        <v>2.59511256946379</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>4.122881758883809</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.917350000682992</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-1.915057255987808</v>
+        <v>-4.431898690876984</v>
       </c>
       <c r="E1959" t="n">
-        <v>2.150970673974121</v>
+        <v>0.9244770862401623</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.008480245722502167</v>
+        <v>-0.3556777965462279</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.912261853249491</v>
+        <v>2.484186308976966</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.972913432880422</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.917350000682992</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-1.915685550365793</v>
+        <v>-4.533096472314156</v>
       </c>
       <c r="E1960" t="n">
-        <v>2.150719356222928</v>
+        <v>0.8832018955617946</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.008480245722502167</v>
+        <v>-0.4240866100915471</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.912261853249491</v>
+        <v>2.442344942746276</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.976175639935069</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.914949962237309</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-1.883209964195021</v>
+        <v>-4.500620886143384</v>
       </c>
       <c r="E1961" t="n">
-        <v>2.161309552245553</v>
+        <v>0.8937920915844204</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.008480245722502167</v>
+        <v>-0.4240866100915471</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.909861814803807</v>
+        <v>2.439944904300593</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.980114421497717</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.911474681445553</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-1.864171836487723</v>
+        <v>-4.481582758436087</v>
       </c>
       <c r="E1962" t="n">
-        <v>2.165449522536717</v>
+        <v>0.8979320618755842</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.06666385705369671</v>
+        <v>-0.4822702214227417</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.871476367213336</v>
+        <v>2.401559456710121</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>4.001668451250868</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
-        <v>3.089056550384234</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-1.895298467638341</v>
+        <v>-4.512709389586705</v>
       </c>
       <c r="E1963" t="n">
-        <v>2.33058073901515</v>
+        <v>1.063063278354017</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.06666385705369671</v>
+        <v>-0.4822702214227417</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.049058236152016</v>
+        <v>2.579141325648802</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.993051340187479</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>3.089889879370368</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-1.947618848239133</v>
+        <v>-4.565029770187497</v>
       </c>
       <c r="E1964" t="n">
-        <v>2.310485915760967</v>
+        <v>1.042968455099834</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.03171699704482456</v>
+        <v>-0.4473233614138695</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.070859681143473</v>
+        <v>2.600942770640259</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>4.14365685279531</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>3.095898409767293</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-2.094150012231326</v>
+        <v>-4.709352676112416</v>
       </c>
       <c r="E1965" t="n">
-        <v>2.257881980561016</v>
+        <v>0.9912478231267925</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.03171699704482456</v>
+        <v>-0.4473233614138695</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.076868211540399</v>
+        <v>2.606951301037185</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>4.14365685279531</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.095898409767293</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-2.094150012231326</v>
+        <v>-4.561609705877413</v>
       </c>
       <c r="E1966" t="n">
-        <v>2.257881980561016</v>
+        <v>1.129497659012816</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.03171699704482456</v>
+        <v>-0.2795160041789864</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.076868211540399</v>
+        <v>2.786788363170137</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>4.14365685279531</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.095898409767293</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-2.094150012231326</v>
+        <v>-4.663624388408635</v>
       </c>
       <c r="E1967" t="n">
-        <v>2.257881980561016</v>
+        <v>1.091485407531808</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.03171699704482456</v>
+        <v>-0.2795160041789864</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.076868211540399</v>
+        <v>2.789581984701618</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>4.14365685279531</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.095898409767293</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-2.094150012231326</v>
+        <v>-4.527015044314542</v>
       </c>
       <c r="E1968" t="n">
-        <v>2.257881980561016</v>
+        <v>1.146791493561103</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.03171699704482456</v>
+        <v>-0.1429066600848939</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.076868211540399</v>
+        <v>2.872209939549732</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>4.079055421818879</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.095898409767293</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-2.100192050616473</v>
+        <v>-4.669780377137192</v>
       </c>
       <c r="E1969" t="n">
-        <v>2.255465165206957</v>
+        <v>1.088765837172154</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.03171699704482456</v>
+        <v>-0.2856719929075443</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.076868211540399</v>
+        <v>2.785631216596252</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>4.148178263726688</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.162233963564114</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-2.037894051840351</v>
+        <v>-4.60748237836107</v>
       </c>
       <c r="E1970" t="n">
-        <v>2.346719918514227</v>
+        <v>1.180020590479423</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.03171699704482456</v>
+        <v>-0.2856719929075443</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.14320376533722</v>
+        <v>2.851966770393072</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>4.112180699617269</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.870814835953512</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.027764882831608</v>
+        <v>-4.405692180695912</v>
       </c>
       <c r="E1971" t="n">
-        <v>2.059352458507122</v>
+        <v>0.9693175419348847</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.02296783088528065</v>
+        <v>-0.08765380073838991</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.857034137422344</v>
+        <v>2.679358558083963</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>4.122777641260166</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.870814835953512</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.03088929876369</v>
+        <v>-4.345801499053318</v>
       </c>
       <c r="E1972" t="n">
-        <v>2.058102692134289</v>
+        <v>1.063564046914097</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.02296783088528065</v>
+        <v>-0.02776311909579643</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.857034137422344</v>
+        <v>2.785583199391694</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>4.130842596346223</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.885442572069556</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.127708257127904</v>
+        <v>-4.443542043678293</v>
       </c>
       <c r="E1973" t="n">
-        <v>2.034002844904647</v>
+        <v>1.039095565180151</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.04049972060132079</v>
+        <v>-0.04365239722877662</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.861142739708764</v>
+        <v>2.79067736862795</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>4.112440231527782</v>
+        <v>3.831231332909034</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.885442572069556</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-2.128013845828054</v>
+        <v>-4.619879803801222</v>
       </c>
       <c r="E1974" t="n">
-        <v>2.034002844904647</v>
+        <v>0.9670964419556509</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.04049972060132079</v>
+        <v>-0.219990157351706</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.861142739708764</v>
+        <v>2.683410693378864</v>
       </c>
     </row>
   </sheetData>
